--- a/output/full_scan/batch_seq1_2026-10-22.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-22.xlsx
@@ -440,11 +440,11 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>925.2498612687076</v>
+        <v>1160.249861268707</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>27.95</v>
@@ -552,29 +552,29 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>67.22819397204944</v>
+        <v>67.22819401833083</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>50.98827055991249</v>
+        <v>50.98827078081172</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.885756429607231</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1247669718155259</v>
+        <v>0.1247669717314016</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>865.8143867555917</v>
+        <v>1130.814386755592</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>38.55</v>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>74.65694166704284</v>
+        <v>74.65694148261387</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>35.20061172888827</v>
+        <v>35.20061183568823</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.509864838249063</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,51 +623,51 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1784100705883634</v>
+        <v>0.178410070576341</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1516</v>
+        <v>1103</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>854</v>
+        <v>945.9754084294111</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>18.55</v>
+        <v>13.6</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>72.81261402898284</v>
+        <v>67.50565610259397</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>16.81551510010855</v>
+        <v>40.84737949354994</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.434070040980664</v>
+        <v>2.697540842941109</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.5360087806631579</v>
+        <v>0.03878559625934105</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1315</v>
+        <v>1216</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>768.2319672952124</v>
+        <v>920.0120406862944</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>67.02608799337834</v>
+        <v>66.83291417447336</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>50.93368222201877</v>
+        <v>26.83188236739417</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.134148269745486</v>
+        <v>0.8012040686294437</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.0452511197905141</v>
+        <v>0.4582317267078517</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1103</v>
+        <v>1569</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>755.9754084294111</v>
+        <v>888.0263552520576</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13.6</v>
+        <v>86.2</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>67.50565615535274</v>
+        <v>75.90264241624436</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>40.84737951664838</v>
+        <v>67.32218148872418</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.697540842941109</v>
+        <v>2.675067735922812</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0387855962713589</v>
+        <v>0.7106369435236903</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1569</v>
+        <v>1528</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>748.0263552520576</v>
+        <v>881.1465846849743</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>86.2</v>
+        <v>25.9</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>75.90264248527357</v>
+        <v>61.21968079438652</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>67.32218144272869</v>
+        <v>31.86824647567126</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.675067735922812</v>
+        <v>4.318140680598007</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,11 +835,11 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.7106369435957998</v>
+        <v>-0.01683316871074081</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>731.4761906920767</v>
+        <v>871.4761906920767</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>16.6</v>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>64.64530954161691</v>
+        <v>64.64530955491284</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.88550412386146</v>
+        <v>22.88550414344115</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>5.107305877482982</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,48 +888,48 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2264940050788846</v>
+        <v>0.2264940050308146</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1528</v>
+        <v>1516</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>701.1465846849743</v>
+        <v>854</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>25.9</v>
+        <v>18.55</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>61.21968077265033</v>
+        <v>72.81261402898284</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>31.86824649438087</v>
+        <v>16.81551510010856</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.318140680598007</v>
+        <v>5.434070040980663</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.0168331685304861</v>
+        <v>0.5360087806822283</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1456</v>
+        <v>1315</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>689.6980198868627</v>
+        <v>823.2319672952124</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>15.4</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>58.68973244865094</v>
+        <v>67.02608781183133</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>22.52493955663527</v>
+        <v>50.93368224852669</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.899879554683425</v>
+        <v>2.134148269745486</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.0313405623194742</v>
+        <v>-0.0452511197424359</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1216</v>
+        <v>1416</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>665.0120406862944</v>
+        <v>792.6375662333867</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>13.25</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>66.83291413750496</v>
+        <v>75.48451859660825</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.83188243944898</v>
+        <v>44.7818591829032</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8012040686294437</v>
+        <v>0.7015148824678775</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.4582317267799667</v>
+        <v>0.09727343412723777</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1416</v>
+        <v>1456</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>627.6375662333867</v>
+        <v>744.6980198868627</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13.25</v>
+        <v>15.4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>75.48451861785465</v>
+        <v>58.68973236823521</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>44.7818591829032</v>
+        <v>22.52493958528356</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.7015148824678775</v>
+        <v>1.899879554683425</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0972734341032029</v>
+        <v>-0.03134056231947421</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1321</v>
+        <v>1477</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>625.5106503377339</v>
+        <v>740.2601889428227</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>34.95</v>
+        <v>209</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>64.61188620499956</v>
+        <v>63.94408705260311</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>29.49881624290268</v>
+        <v>33.41179717905271</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.8017099990846154</v>
+        <v>0.6783956063873652</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1898613964844717</v>
+        <v>1.147858199281586</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1312</v>
+        <v>1476</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>611.7590176431602</v>
+        <v>728.5596351425534</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>14.8</v>
+        <v>324.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>47.16151897071516</v>
+        <v>66.41068528399984</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>41.3698027950925</v>
+        <v>37.8620539103713</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.4620147805487044</v>
+        <v>0.4762559980374482</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,11 +1206,11 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.1796110411229116</v>
+        <v>4.134197855375534</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>610.1870478648734</v>
+        <v>665.1870478648735</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>73</v>
@@ -1244,7 +1244,7 @@
         <v>50.31850582068898</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>34.3493514040558</v>
+        <v>34.34935146180015</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.5959525816474684</v>
@@ -1253,37 +1253,37 @@
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.4444131549530734</v>
+        <v>-0.4444131549050043</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1303</v>
+        <v>1236</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>604.31307372087</v>
+        <v>641.3269049936374</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>301</v>
+        <v>25.95</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.56586680208852</v>
+        <v>56.1484781941305</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>43.51910231520445</v>
+        <v>20.49943886509741</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.047428895921066</v>
+        <v>0.6430549803829058</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-1.577043196961135</v>
+        <v>0.03910150812958971</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>601.0098111719967</v>
+        <v>636.3767173989937</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>55.17942646922257</v>
+        <v>48.88576558020389</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>26.34376175479601</v>
+        <v>23.53005489333985</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.4785622234440209</v>
+        <v>1.784399689079536</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1284552824824374</v>
+        <v>-0.01664002015503629</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1301</v>
+        <v>1457</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>590.7225723372153</v>
+        <v>625.3482834581496</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>73.8</v>
+        <v>14.55</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>51.61101266922207</v>
+        <v>54.92073618613777</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>38.35204913367968</v>
+        <v>16.6983919890933</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6013248262975751</v>
+        <v>0.5315720086149386</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.502189941723941</v>
+        <v>0.02338600392438938</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>587.9113426968719</v>
+        <v>620.29575185482</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>19.3</v>
+        <v>13.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>54.47681660535991</v>
+        <v>52.57465550717582</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>37.83509264550975</v>
+        <v>21.89920479298087</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5334352961232455</v>
+        <v>0.3663848025068586</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0141564455225992</v>
+        <v>-0.01318895398077691</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1558</v>
+        <v>1303</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>585.1942445734639</v>
+        <v>619.345781596306</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>113</v>
+        <v>301</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>55.11004136494972</v>
+        <v>56.56586679743685</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>23.35014564415632</v>
+        <v>43.51910231715581</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.8490513455903952</v>
+        <v>1.052114640484283</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.2353773387240849</v>
+        <v>-1.577043196913085</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1323</v>
+        <v>1402</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>581.3767173989937</v>
+        <v>610.9031575670751</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>21.5</v>
+        <v>28.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>48.88576560257627</v>
+        <v>54.51453730355608</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>23.53005489333985</v>
+        <v>19.9678902238398</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.784399689079536</v>
+        <v>0.9038954883700848</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.0166400201670544</v>
+        <v>0.02756989543045099</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1477</v>
+        <v>1445</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>570.2601889428225</v>
+        <v>575.5349375040082</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>63.9440872045707</v>
+        <v>44.19179884816317</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>33.41179708870771</v>
+        <v>31.8314960356828</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6783956063873652</v>
+        <v>1.186265452776034</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.147858198440379</v>
+        <v>0.01087099059645795</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1440</v>
+        <v>1312</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>565.2957518548201</v>
+        <v>566.7590176431602</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>13.9</v>
+        <v>14.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.57465552371228</v>
+        <v>47.16151897971363</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>21.89920475338675</v>
+        <v>41.36980284747396</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3663848025068585</v>
+        <v>0.4620147805487044</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.0131889539807769</v>
+        <v>-0.1796110411469446</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1236</v>
+        <v>1321</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>561.3269049936374</v>
+        <v>565.510650337734</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>25.95</v>
+        <v>34.95</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>56.14847826135128</v>
+        <v>64.61188617286926</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20.49943891284925</v>
+        <v>29.49881619415126</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6430549803829058</v>
+        <v>0.8017099990846154</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0391015080334518</v>
+        <v>0.18986139654456</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1402</v>
+        <v>1470</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>555.9031575670751</v>
+        <v>561.0783603551657</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>28.9</v>
+        <v>24.65</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>54.51453749006029</v>
+        <v>52.15532288858483</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>19.96789027252851</v>
+        <v>12.11643028644397</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.9038954883700848</v>
+        <v>0.2489099817051164</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0275698953222924</v>
+        <v>0.07544777278270004</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1457</v>
+        <v>1563</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>545.3482834581496</v>
+        <v>553.0014423392493</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>14.55</v>
+        <v>76.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>54.92073623534467</v>
+        <v>47.28923752711714</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>16.69839196981113</v>
+        <v>39.49940665830184</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5315720086149386</v>
+        <v>0.5643919099444266</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0233860039003561</v>
+        <v>-0.9097498069136005</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1476</v>
+        <v>1301</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>538.5596351425534</v>
+        <v>545.7225723372153</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>324.5</v>
+        <v>73.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>66.41068517733299</v>
+        <v>51.61101266922207</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>37.86205382214528</v>
+        <v>38.3520491998043</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4762559980374482</v>
+        <v>0.6013248262975751</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>4.13419785693778</v>
+        <v>-0.5021899417599913</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1563</v>
+        <v>1203</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>538.0014423392493</v>
+        <v>535.7105702311541</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>76.7</v>
+        <v>43.15</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>47.28923752711714</v>
+        <v>48.43272904964675</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>39.49940652169693</v>
+        <v>10.0096741267398</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5643919099444266</v>
+        <v>0.9006456250374378</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.9097498066870447</v>
+        <v>0.01340311611296929</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, avoid_chase, hist_turn_positive, stronger_than_market, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1418</v>
+        <v>1310</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>514.4725280876993</v>
+        <v>534.0497302347534</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>17.9</v>
+        <v>9.59</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>43.31295755745024</v>
+        <v>51.80010973807624</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>37.78314313421867</v>
+        <v>45.89465837480962</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.5280489279729099</v>
+        <v>0.5490835262969375</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.0825021930735433</v>
+        <v>-0.04145491806589163</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1409</v>
+        <v>1319</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>511.2402254742011</v>
+        <v>531.0098111719967</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>24.9</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>47.63970803254432</v>
+        <v>55.1794265490582</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>24.46382272420101</v>
+        <v>26.34376177058579</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4005305714480796</v>
+        <v>0.4785622234440209</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.099455188505255</v>
+        <v>0.1284552826026084</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1313</v>
+        <v>1434</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>508.3984578038276</v>
+        <v>527.9113426968719</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12.2</v>
+        <v>19.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>45.52996761612221</v>
+        <v>54.47681658305314</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>28.72846172371656</v>
+        <v>37.83509269077872</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5969970290769615</v>
+        <v>0.5334352961232455</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.0789513554492286</v>
+        <v>0.01415644551058193</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1470</v>
+        <v>1558</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>506.0783603551657</v>
+        <v>525.1942445734639</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>24.65</v>
+        <v>113</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>52.15532361794371</v>
+        <v>55.11004129299651</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>12.11643129271038</v>
+        <v>23.35014564415632</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.2489099817051163</v>
+        <v>0.8490513455903952</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.07544776804788229</v>
+        <v>-0.2353773387000584</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1308</v>
+        <v>1560</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>499.0674774523511</v>
+        <v>517.5159755642122</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>13.75</v>
+        <v>846</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>40.56629876584488</v>
+        <v>42.08095388467736</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>31.68460791563301</v>
+        <v>31.95696279954685</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7366654226485709</v>
+        <v>0.8192230758207769</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.1081335552466996</v>
+        <v>-25.0275619679547</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1310</v>
+        <v>1210</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>484.0497302347533</v>
+        <v>510.6090786428364</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9.59</v>
+        <v>51.3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>51.80010968626064</v>
+        <v>43.43331045476441</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45.89465835210204</v>
+        <v>23.18524993762747</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5490835262969375</v>
+        <v>0.5782598888956022</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.0414549180514715</v>
+        <v>0.02834004245045718</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1203</v>
+        <v>1316</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>480.710570231154</v>
+        <v>502.5262142618887</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>43.15</v>
+        <v>10.2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>48.43272909839818</v>
+        <v>41.03846279133447</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>10.00967416812288</v>
+        <v>13.76842119257366</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.9006456250374378</v>
+        <v>3.710012438565919</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0134031160168271</v>
+        <v>-0.02153990639402967</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, williams_r_recovery</t>
+          <t>volume_break, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1309</v>
+        <v>1513</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>473.8168789351852</v>
+        <v>495.7151263707709</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>13.55</v>
+        <v>160</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>43.73047504787633</v>
+        <v>38.6869199916101</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>34.41011025611512</v>
+        <v>11.42811229698812</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5287290176459353</v>
+        <v>0.6214000071743462</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.0972460706488916</v>
+        <v>-0.8305585320714264</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1325</v>
+        <v>1532</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>470.7518091543565</v>
+        <v>480.930952705536</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>26.85</v>
+        <v>21.75</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>46.66568620342301</v>
+        <v>43.03933676744486</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>29.72973505573392</v>
+        <v>21.01873653586321</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.22416733817671</v>
+        <v>0.7439184876399714</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.1746697744329102</v>
+        <v>0.0154379133416423</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1304</v>
+        <v>1418</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>463.8011036693731</v>
+        <v>474.4725280876992</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>12.65</v>
+        <v>17.9</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>47.43459294169568</v>
+        <v>43.31295781375929</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>36.48648904604192</v>
+        <v>37.7831434588695</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.4503480288655173</v>
+        <v>0.5280489279729099</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.0500854523317108</v>
+        <v>-0.0825021932778363</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1560</v>
+        <v>1409</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>462.5159755642122</v>
+        <v>471.2402254742011</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>846</v>
+        <v>24.9</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>42.08095390525968</v>
+        <v>47.63970805635945</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>31.95696279954685</v>
+        <v>24.46382271990138</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.8192230758207769</v>
+        <v>0.4005305714480796</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-25.02756196843553</v>
+        <v>-0.0994551885893783</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1210</v>
+        <v>1541</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>435.6090786428365</v>
+        <v>461.2596177740492</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>51.3</v>
+        <v>20</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>43.43331038718329</v>
+        <v>50.53173033559301</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>23.18524990578156</v>
+        <v>10.6238493478604</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5782598888956022</v>
+        <v>2.851818566293085</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0283400425225591</v>
+        <v>0.07044048162124739</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1445</v>
+        <v>1232</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>410.5349375040083</v>
+        <v>452.6368368916584</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>44.19179890701865</v>
+        <v>45.90484693019192</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>31.83149609972683</v>
+        <v>16.09166015874677</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.186265452776034</v>
+        <v>0.9830428177862458</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0108709905604065</v>
+        <v>0.02387868821441951</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1314</v>
+        <v>1537</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>408.030090417311</v>
+        <v>450.6665734929202</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>8.51</v>
+        <v>115</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>44.89434105970374</v>
+        <v>47.91113729098156</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>34.77860004246716</v>
+        <v>20.7706201131799</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5454585161494226</v>
+        <v>1.046944844780225</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.0738363473554986</v>
+        <v>0.2491873195380336</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1524</v>
+        <v>1313</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>406.6733874472914</v>
+        <v>448.3984578038276</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>26.65</v>
+        <v>12.2</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>49.59765323134797</v>
+        <v>45.52996769037252</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>28.4395936734038</v>
+        <v>28.72846170757203</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5393660494386591</v>
+        <v>0.5969970290769615</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0535294168871297</v>
+        <v>-0.07895135550931476</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1232</v>
+        <v>1453</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>397.6368368916584</v>
+        <v>446.1275552542835</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>154</v>
+        <v>11.05</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45.90484706070863</v>
+        <v>53.48868763967705</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16.09166007544478</v>
+        <v>17.83851628019204</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.9830428177862458</v>
+        <v>0.94351239308079</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0238786880942449</v>
+        <v>0.01672001997694503</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, kd_golden_cross, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1537</v>
+        <v>1504</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>395.6665734929202</v>
+        <v>446.0184672060134</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>115</v>
+        <v>69.7</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>47.91113738908143</v>
+        <v>48.90119524052107</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>20.77062015729866</v>
+        <v>15.21305720695588</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.046944844780225</v>
+        <v>0.9174516046541222</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.2491873195380336</v>
+        <v>-0.07487907053995242</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1459</v>
+        <v>1308</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>382.7880615437255</v>
+        <v>439.0674774523511</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>18</v>
+        <v>13.75</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>58.47485537900773</v>
+        <v>40.5662988135626</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>64.22641119598626</v>
+        <v>31.68460792312481</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.1763728741855054</v>
+        <v>0.7366654226485709</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1436329391517512</v>
+        <v>-0.1081335552827524</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1541</v>
+        <v>1459</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>381.2596177740493</v>
+        <v>437.7880615437255</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>50.53173035196909</v>
+        <v>58.47485539775608</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>10.62384930886277</v>
+        <v>64.22641136979226</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.851818566293085</v>
+        <v>0.1763728741855054</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0704404816452808</v>
+        <v>-0.1436329391723479</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1225</v>
+        <v>1215</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>377.439291932987</v>
+        <v>434.7350949140956</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>23.8</v>
+        <v>107</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>41.10513918952</v>
+        <v>51.61039192268831</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>27.25126426591207</v>
+        <v>13.1423371512287</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.9228546604900441</v>
+        <v>0.5422154285748083</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,11 +3008,11 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0125159897431927</v>
+        <v>0.2348333998358355</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>374.6689866539822</v>
+        <v>429.6689866539822</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>28</v>
@@ -3046,7 +3046,7 @@
         <v>48.07826756401787</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.37057201315988</v>
+        <v>13.37057198700673</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.3545110359982702</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0010848044465943</v>
+        <v>-0.001084804446594312</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1467</v>
+        <v>1522</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>374.0382993950906</v>
+        <v>426.2256036612502</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>7.91</v>
+        <v>26.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>41.6418753849338</v>
+        <v>48.37519985326762</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15.90290011918183</v>
+        <v>13.52240630057613</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4808313018780661</v>
+        <v>1.036533289575128</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0125102486062306</v>
+        <v>0.08582274837837976</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1513</v>
+        <v>1325</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>370.7151263707709</v>
+        <v>420.7518091543565</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>160</v>
+        <v>26.85</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>38.68692037632304</v>
+        <v>46.66568627613604</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>11.42811220976796</v>
+        <v>29.72973539784932</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6214000071743462</v>
+        <v>0.2241673381767101</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.8305585331529752</v>
+        <v>-0.1746697746732524</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1453</v>
+        <v>1309</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>366.1275552542835</v>
+        <v>413.8168789351852</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>11.05</v>
+        <v>13.55</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>53.48868767625923</v>
+        <v>43.7304750753824</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>17.83851624934836</v>
+        <v>34.41011017552491</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.94351239308079</v>
+        <v>0.5287290176459353</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0167200199889635</v>
+        <v>-0.09724607069696029</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, cci_momentum, mfi_strong</t>
+          <t>avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1305</v>
+        <v>1472</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>365.7919122020854</v>
+        <v>408.0867869331105</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>12.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>47.80496239578044</v>
+        <v>52.62412261036246</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>32.49655259353178</v>
+        <v>6.444766285013309</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.407632821778858</v>
+        <v>0.4875341668806329</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0466407674049966</v>
+        <v>-0.2529556236433477</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1339</v>
+        <v>1304</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>362.6737021198175</v>
+        <v>403.8011036693731</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>41.2</v>
+        <v>12.65</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>33.01850205069202</v>
+        <v>47.43459299079519</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>30.00260837290816</v>
+        <v>36.48648910387239</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.097233452453498</v>
+        <v>0.4503480288655173</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0642467854846446</v>
+        <v>-0.05008545236776255</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1455</v>
+        <v>1104</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>362.4454568452755</v>
+        <v>401.3248097261706</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>9.75</v>
+        <v>27</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45.35651939335379</v>
+        <v>53.39231253641537</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>33.07498638181296</v>
+        <v>17.52592621661223</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3913103384926285</v>
+        <v>1.110544920475465</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0451300161776417</v>
+        <v>0.01060223128731803</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1504</v>
+        <v>1517</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>346.0184672060134</v>
+        <v>399.3025367340296</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>69.7</v>
+        <v>10.3</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.90119525771829</v>
+        <v>43.39820073397857</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>15.21305718754079</v>
+        <v>23.09991949363018</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9174516046541222</v>
+        <v>1.690104392507155</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.07487907041978201</v>
+        <v>0.02316421767544768</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1517</v>
+        <v>1110</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>344.3025367340297</v>
+        <v>396.6654492197475</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>10.3</v>
+        <v>14.4</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>43.39820069524713</v>
+        <v>39.32029416923925</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>23.09991942694419</v>
+        <v>44.38443207812463</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.690104392507155</v>
+        <v>0.26527737954334</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0231642176754476</v>
+        <v>0.03832927483297471</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1110</v>
+        <v>1213</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>341.6654492197475</v>
+        <v>388.8848264185904</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>14.4</v>
+        <v>7.21</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>39.32029416923925</v>
+        <v>51.47628258805543</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>44.38443223150122</v>
+        <v>9.195139657620912</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.26527737954334</v>
+        <v>1.213837046724031</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0383292748209581</v>
+        <v>-0.06219018997165694</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1316</v>
+        <v>1473</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>338.1544459138281</v>
+        <v>388.7671418522369</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>10.2</v>
+        <v>18.85</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>41.03846283327425</v>
+        <v>34.97952203631272</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.76842113983193</v>
+        <v>44.88680352163931</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7728356037598558</v>
+        <v>1.444803384559349</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0215399063820133</v>
+        <v>-0.0007838578730914036</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1215</v>
+        <v>1514</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>334.7350949140958</v>
+        <v>384.4145656427831</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>107</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>51.61039188518105</v>
+        <v>40.93268048618865</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>13.14233713075826</v>
+        <v>11.74183229638204</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5422154285748083</v>
+        <v>0.7215689761067196</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2348333999560113</v>
+        <v>-0.4176754123772879</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1473</v>
+        <v>1535</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>333.7671418522369</v>
+        <v>382.2070150965523</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>18.85</v>
+        <v>45.8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>34.97952225512866</v>
+        <v>51.10893499769771</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>44.88680352410155</v>
+        <v>19.23056757529915</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.444803384559349</v>
+        <v>1.107740551194117</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0007838578730914</v>
+        <v>0.008362932128092672</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1535</v>
+        <v>1307</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>327.2070150965523</v>
+        <v>379.0206616479385</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>45.8</v>
+        <v>31</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.10893526368163</v>
+        <v>49.60348735734944</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>19.23056750333913</v>
+        <v>11.84462246610018</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.107740551194117</v>
+        <v>1.268534588509361</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.008362932031958</v>
+        <v>-0.03824517284626756</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1104</v>
+        <v>1451</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>321.3248097261706</v>
+        <v>375.7268237757937</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>53.39231265929208</v>
+        <v>43.05829126220716</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>17.52592617155567</v>
+        <v>12.8267462131565</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.110544920475465</v>
+        <v>0.4001182870078424</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0106022312753007</v>
+        <v>0.003922198414267282</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1451</v>
+        <v>1256</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>320.7268237757937</v>
+        <v>365.8096919290853</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>43.05829137310788</v>
+        <v>42.37011668304041</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.82674612508569</v>
+        <v>8.319428195744438</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4001182870078423</v>
+        <v>0.4600557741757824</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0039221984142672</v>
+        <v>0.2191739783363484</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1419</v>
+        <v>1468</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>315.663697597333</v>
+        <v>360.0548654552368</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>63.5</v>
+        <v>13.25</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>37.04555221823462</v>
+        <v>50.73405679072533</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.17341351210402</v>
+        <v>7.973975386292214</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.3550157074723045</v>
+        <v>0.5975139833209947</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.2656956509161909</v>
+        <v>0.0004004809074422515</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>macd_golden_cross, ema60_gt_ema120, avoid_chase, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1439</v>
+        <v>1314</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>311.8470103394647</v>
+        <v>348.030090417311</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>28.3</v>
+        <v>8.51</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.99084934449761</v>
+        <v>44.89434108506562</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13.79774725079524</v>
+        <v>34.77860012191497</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.009326928468627</v>
+        <v>0.5454585161494226</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.3789605354622124</v>
+        <v>-0.0738363473651118</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1256</v>
+        <v>1524</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>310.8096919290853</v>
+        <v>346.6733874472961</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>166</v>
+        <v>26.65</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>42.37011618499066</v>
+        <v>49.59765327557657</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>8.319428167132838</v>
+        <v>28.4395936734038</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.4600557741757823</v>
+        <v>0.5393660494386591</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.2191739785767255</v>
+        <v>0.05352941674292044</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1514</v>
+        <v>1437</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>309.4145656427938</v>
+        <v>342.8290456541291</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>98.59999999999999</v>
+        <v>31.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>40.93268087554996</v>
+        <v>44.43472543376139</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>11.74183225718146</v>
+        <v>16.63724608769352</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7215689761067196</v>
+        <v>3.841408098733572</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.4176754130983162</v>
+        <v>-0.004043074459428808</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1213</v>
+        <v>1413</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>308.8848264185904</v>
+        <v>339.2653606967882</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>7.21</v>
+        <v>9.43</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.47628320332965</v>
+        <v>54.76490306619252</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>9.195139656056009</v>
+        <v>8.820709995351043</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.213837046724031</v>
+        <v>0.3444450285100885</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.062190189983674</v>
+        <v>0.00996388305984125</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1472</v>
+        <v>1460</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>308.0867869331105</v>
+        <v>331.8788220281783</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>88.59999999999999</v>
+        <v>6.05</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.6241225865031</v>
+        <v>30.27544526690903</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>6.444766106181291</v>
+        <v>28.26196199971221</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4875341668806329</v>
+        <v>0.7234782411867646</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.2529556233549366</v>
+        <v>0.005899539086103342</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1342</v>
+        <v>1443</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>292.7062305274783</v>
+        <v>324.7641975837685</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>96.7</v>
+        <v>22.45</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>31.0681870732337</v>
+        <v>43.36351037534183</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>18.68040897377207</v>
+        <v>16.19488793105122</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.711676728001756</v>
+        <v>0.808491582247074</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.3157175431655195</v>
+        <v>-0.02617305415082732</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1519</v>
+        <v>1225</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>291.6225511311849</v>
+        <v>317.439291932987</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>615</v>
+        <v>23.8</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>33.30214390271676</v>
+        <v>41.1051390941152</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12.716184763978</v>
+        <v>27.25126430947455</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5237464880521181</v>
+        <v>0.9228546604900439</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-7.221732687247922</v>
+        <v>-0.01251598976722607</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1532</v>
+        <v>1467</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>290.9309527055361</v>
+        <v>314.0382993950906</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>21.75</v>
+        <v>7.91</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>43.03933669615611</v>
+        <v>41.64187541071813</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21.01873653586321</v>
+        <v>15.9029000964332</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.7439184876399714</v>
+        <v>0.4808313018780662</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0154379134377797</v>
+        <v>-0.01251024861584429</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1423</v>
+        <v>1475</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>285.7903175838593</v>
+        <v>306.8260899314311</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>34.35</v>
+        <v>25.2</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.30613010887571</v>
+        <v>37.30382887658166</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>8.699330763051309</v>
+        <v>14.48436564886853</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.534455435045157</v>
+        <v>1.663891804908274</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.3750801496305191</v>
+        <v>-0.06593604110046239</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1465</v>
+        <v>1305</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>284.5975812563132</v>
+        <v>305.7919122020854</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>11.45</v>
+        <v>12.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>38.00230925846498</v>
+        <v>47.80496242511996</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>17.17945841791047</v>
+        <v>32.49655271958042</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.103509245009634</v>
+        <v>0.407632821778858</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0039372461096466</v>
+        <v>-0.04664076744104809</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1413</v>
+        <v>1339</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>284.2653606967882</v>
+        <v>302.6737021198174</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>9.43</v>
+        <v>41.2</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>54.76490299437295</v>
+        <v>33.01850191987452</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8.820710012139356</v>
+        <v>30.00260833514157</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3444450285100885</v>
+        <v>1.097233452453498</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.009963883083875601</v>
+        <v>-0.06424678548464469</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1468</v>
+        <v>1455</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>280.0548654552368</v>
+        <v>302.4454568452755</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>13.25</v>
+        <v>9.75</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>50.73405683931346</v>
+        <v>45.35651936976606</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>7.973975392864707</v>
+        <v>33.07498640195481</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5975139833209947</v>
+        <v>0.3913103384926285</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0004004809074422</v>
+        <v>-0.04513001617764176</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1503</v>
+        <v>1410</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>279.8242370895177</v>
+        <v>302.2024308302486</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>192</v>
+        <v>23.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.23756974788368</v>
+        <v>38.48702343291328</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>9.796564224143475</v>
+        <v>7.617536348053889</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8919521866451359</v>
+        <v>0.6271837785975587</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.6151077149869169</v>
+        <v>0.009527175774447116</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>276.8788220281781</v>
+        <v>301.4427551264689</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>6.05</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>30.27544536802804</v>
+        <v>34.86981328212447</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>28.26196198247714</v>
+        <v>25.36638529354557</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.7234782411867646</v>
+        <v>1.395196716124667</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0058995390788928</v>
+        <v>0.000142484817384686</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1443</v>
+        <v>1506</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>269.7641975837685</v>
+        <v>297.8415334679412</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>22.45</v>
+        <v>9.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>43.36351031133334</v>
+        <v>34.23089086729462</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.19488795767953</v>
+        <v>18.41097726197723</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.808491582247074</v>
+        <v>0.7588313416947114</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0261730541147757</v>
+        <v>0.006374188734929884</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1437</v>
+        <v>1463</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>262.8290456541291</v>
+        <v>295.5216132350779</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>31.2</v>
+        <v>17.6</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>44.43472562670475</v>
+        <v>47.12656667669876</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16.63724592465598</v>
+        <v>14.17372294326239</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>3.841408098733572</v>
+        <v>0.9979275133066693</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0040430746276689</v>
+        <v>0.003183945421184692</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1522</v>
+        <v>1515</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>261.2256036612502</v>
+        <v>295.0316251128382</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>26.5</v>
+        <v>27.55</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>48.37519983318866</v>
+        <v>38.48273909190718</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.5224062653494</v>
+        <v>7.946364096848186</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.036533289575128</v>
+        <v>1.141736795086661</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.08582274857065771</v>
+        <v>0.02105877539483614</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1229</v>
+        <v>1525</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>254.9523194066132</v>
+        <v>292.5799654939154</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>39.95</v>
+        <v>62.8</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.65617315991714</v>
+        <v>50.37570354983596</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>17.56211261120774</v>
+        <v>8.071739521147883</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5312389084996308</v>
+        <v>1.591717518967429</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0197066485211868</v>
+        <v>0.273757593606871</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1568</v>
+        <v>1533</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>253.7034867605874</v>
+        <v>291.2791308962231</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>38.25111970632818</v>
+        <v>34.63655180391633</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>22.97816375392077</v>
+        <v>13.61785347832587</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5314132171035814</v>
+        <v>1.992951684169262</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.3378993240669259</v>
+        <v>-0.07171242524689847</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1217</v>
+        <v>1340</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>252.930704552935</v>
+        <v>283.6091950246549</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>4.98</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>29.31252533377124</v>
+        <v>35.74218418674596</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>22.01298822514927</v>
+        <v>11.12301220062339</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.360898114894204</v>
+        <v>1.760919502465495</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0169131256747621</v>
+        <v>-0.01614659393983846</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1475</v>
+        <v>1432</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>251.826089931431</v>
+        <v>280.8215544552968</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>25.2</v>
+        <v>14.9</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>37.30382903698696</v>
+        <v>36.44424957313118</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>14.48436562953212</v>
+        <v>17.67498874108724</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.663891804908274</v>
+        <v>0.5843450739975848</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.06593604114853149</v>
+        <v>-0.007545946936837265</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1444</v>
+        <v>1512</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>251.4544002663449</v>
+        <v>279.9882437346843</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>6.66</v>
+        <v>6.25</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>38.3210173949713</v>
+        <v>48.55393283862234</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>21.88645084873778</v>
+        <v>19.11615589845732</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.001584990708859</v>
+        <v>0.2529138567877762</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.014173959407557</v>
+        <v>0.01236264550437366</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1464</v>
+        <v>1109</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>246.442755126469</v>
+        <v>278.5477045692471</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>9.859999999999999</v>
+        <v>13.05</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>34.86981296201991</v>
+        <v>36.26359413417264</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>25.3663853236172</v>
+        <v>36.43133900512838</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.395196716124667</v>
+        <v>1.110804882276412</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0001424848654537</v>
+        <v>-0.007032436208796455</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1515</v>
+        <v>1324</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>245.0316251128382</v>
+        <v>275.80856825208</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>27.55</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>38.48273899983148</v>
+        <v>40.88061474972265</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>7.946364019189819</v>
+        <v>19.32283006700711</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.141736795086661</v>
+        <v>0.9656777798966892</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0210587752746629</v>
+        <v>-0.002733308688644874</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1521</v>
+        <v>1414</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>244.53663451125</v>
+        <v>272.1628941739328</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>25</v>
+        <v>17.35</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>39.89574370518552</v>
+        <v>43.43434984029913</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>22.60886461612286</v>
+        <v>16.82255517268307</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5399184266849736</v>
+        <v>1.169022783709383</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.094274399543068</v>
+        <v>0.04150184483052016</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1447</v>
+        <v>1108</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>242.9010162276014</v>
+        <v>271.2073266115698</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>6.22</v>
+        <v>10.95</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>37.36424645863133</v>
+        <v>30.25948870534828</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>23.51100443738882</v>
+        <v>34.58904658987375</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.122346288879889</v>
+        <v>0.6038300506478742</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0109731484900104</v>
+        <v>0.009929514370426273</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1506</v>
+        <v>1474</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>242.8415334679412</v>
+        <v>271.0133949067844</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>9.5</v>
+        <v>9.98</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>34.23089000936827</v>
+        <v>48.73350234500433</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>18.41097726197723</v>
+        <v>12.06062427980989</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7588313416947114</v>
+        <v>0.2324904627064758</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0063741887589658</v>
+        <v>0.0004678325356735243</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1231</v>
+        <v>1539</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>241.8618183480428</v>
+        <v>269.6913430748821</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>74.3</v>
+        <v>15.3</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>20.77512254949276</v>
+        <v>35.73061798298103</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>36.12172658674661</v>
+        <v>30.35315962862844</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.7811844471055056</v>
+        <v>1.253583202524372</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.3064339958445623</v>
+        <v>-0.02073921303832876</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1442</v>
+        <v>1201</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>241.212642862778</v>
+        <v>264.6388945065559</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>26</v>
+        <v>11.45</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>35.1763527387141</v>
+        <v>40.22978147575908</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>31.2451995620087</v>
+        <v>40.17210484007352</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3988081913507854</v>
+        <v>1.398569821767086</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0093877317193523</v>
+        <v>0.02320298581588753</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1463</v>
+        <v>1419</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>240.5216132350779</v>
+        <v>255.6636975973335</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>17.6</v>
+        <v>63.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>47.12656676061094</v>
+        <v>37.04555230374353</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14.17372294326239</v>
+        <v>15.17341360682296</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.9979275133066692</v>
+        <v>0.3550157074723045</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0031839454211846</v>
+        <v>-0.2656956510363521</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1533</v>
+        <v>1439</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>236.2791308962234</v>
+        <v>251.8470103394647</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>29</v>
+        <v>28.3</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>34.63655188503753</v>
+        <v>50.99084933536099</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.61785345226362</v>
+        <v>13.7977472693179</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.992951684169262</v>
+        <v>1.009326928468627</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0717124252348775</v>
+        <v>0.3789605355343183</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1454</v>
+        <v>1582</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>232.622065604318</v>
+        <v>247.0535719787309</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>12</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>40.41731715180272</v>
+        <v>44.13305884213477</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>20.9978494286116</v>
+        <v>13.70675871013541</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.9062851370223992</v>
+        <v>1.947212138697003</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0527931474013277</v>
+        <v>0.01770878511476737</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>230.2109922092429</v>
+        <v>246.9234449213294</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>38.74514950821352</v>
+        <v>31.78735351417725</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.09814364471588</v>
+        <v>24.10910253017152</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.1507890554741108</v>
+        <v>0.8609879271902744</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-1.040451370748093</v>
+        <v>-0.0827839458783165</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1340</v>
+        <v>1219</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>228.6091950246549</v>
+        <v>244.4673889297369</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>4.98</v>
+        <v>11.2</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>35.74218410026226</v>
+        <v>46.32820835490458</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.1230122188616</v>
+        <v>13.4304674303655</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.760919502465495</v>
+        <v>0.4522391118085424</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0161465939254181</v>
+        <v>-0.00430651056415611</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1109</v>
+        <v>1220</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>223.5477045692472</v>
+        <v>242.5397055736768</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>13.05</v>
+        <v>10.7</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>36.26359398682085</v>
+        <v>38.27339323710818</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>36.43133916764624</v>
+        <v>18.31161572055116</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.110804882276412</v>
+        <v>0.6835417548362436</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0070324362208159</v>
+        <v>-0.0151198826557355</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1410</v>
+        <v>1527</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>222.2024308302486</v>
+        <v>234.3729286086376</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>23.5</v>
+        <v>32.05</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>38.4870234575392</v>
+        <v>37.1768262506079</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>7.617536507132761</v>
+        <v>10.08564669800517</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6271837785975587</v>
+        <v>0.7015852638147142</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0095271757504113</v>
+        <v>-0.03795846211734499</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1324</v>
+        <v>1342</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>220.8085682520801</v>
+        <v>232.7062305274775</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>9.859999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.88061474972265</v>
+        <v>31.06818699288814</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>19.32283027768369</v>
+        <v>18.6804090335585</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.9656777798966892</v>
+        <v>1.711676728001756</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0027333087487326</v>
+        <v>-0.3157175432616578</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1414</v>
+        <v>1519</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>217.1628941739327</v>
+        <v>231.6225511311858</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>17.35</v>
+        <v>615</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>43.4343496667494</v>
+        <v>33.3021436707953</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>16.82255517268307</v>
+        <v>12.71618485340681</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.169022783709383</v>
+        <v>0.5237464880521181</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0415018449540938</v>
+        <v>-7.221732680277878</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1108</v>
+        <v>1338</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>216.2073266115697</v>
+        <v>230.6494101686914</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>10.95</v>
+        <v>14.45</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>30.25948890338028</v>
+        <v>41.53060149759695</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>34.58904641126615</v>
+        <v>24.7414287256596</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.6038300506478742</v>
+        <v>0.4976793908482958</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0099295143463907</v>
+        <v>-0.05860629733813769</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1474</v>
+        <v>1423</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>216.0133949067844</v>
+        <v>225.7903175838593</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>9.98</v>
+        <v>34.35</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.73350275782867</v>
+        <v>51.30613010717237</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>12.06062426112254</v>
+        <v>8.699330794350457</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.2324904627064758</v>
+        <v>1.534455435045157</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0004678325116385</v>
+        <v>0.37508014966658</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1539</v>
+        <v>1465</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>214.6913430748829</v>
+        <v>224.5975812563132</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>15.3</v>
+        <v>11.45</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>35.7306180841763</v>
+        <v>38.00230958774962</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>30.35315973736345</v>
+        <v>17.1794584639681</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.253583202524372</v>
+        <v>2.103509245009634</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0207392130142928</v>
+        <v>0.003937246013506521</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1307</v>
+        <v>1503</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>214.0206616479385</v>
+        <v>219.8242370895177</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>49.60348739273598</v>
+        <v>42.23756923185449</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>11.8446224542623</v>
+        <v>9.796564228807661</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.268534588509361</v>
+        <v>0.8919521866451359</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0382451727741671</v>
+        <v>-0.6151077118624446</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1525</v>
+        <v>1446</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>212.5799654939155</v>
+        <v>216.5131984072283</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>62.8</v>
+        <v>13.3</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>50.37570353951952</v>
+        <v>39.13823099058795</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>8.0717393902308</v>
+        <v>12.03879514806371</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.591717518967429</v>
+        <v>1.036579126426111</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.2737575938231857</v>
+        <v>0.001762770061251223</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1201</v>
+        <v>1438</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>209.6388945065559</v>
+        <v>205.4639235773386</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>11.45</v>
+        <v>21.55</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>40.22978147575908</v>
+        <v>47.08398958909182</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>40.17210489530494</v>
+        <v>7.494613851272913</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.398569821767086</v>
+        <v>0.7250902417192936</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0232029858279045</v>
+        <v>0.009910535291324934</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1512</v>
+        <v>1442</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>199.9882437346843</v>
+        <v>201.2126428627774</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>6.25</v>
+        <v>26</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>48.55393282930263</v>
+        <v>35.17635308601176</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>19.1161558817489</v>
+        <v>31.24519957971321</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.2529138567877761</v>
+        <v>0.3988081913507854</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0123626455067769</v>
+        <v>0.009387731286727874</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1441</v>
+        <v>1229</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>199.3426903358456</v>
+        <v>194.9523194066126</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0</v>
+        <v>39.95</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,49 +6329,49 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>8.10161410686419</v>
+        <v>43.65617295722609</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>32.2621861209558</v>
+        <v>17.56211267146425</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.0812640794183337</v>
+        <v>0.5312389084996308</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.6328213617975743</v>
+        <v>0.01970664848514056</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1218</v>
+        <v>1568</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>197.2897255083023</v>
+        <v>193.7034867605874</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>14.25</v>
+        <v>28.9</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>44.76535376608174</v>
+        <v>38.25111979138109</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>6.053047171978013</v>
+        <v>22.97816376004682</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.8043434055369213</v>
+        <v>0.5314132171035814</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.021493499469037</v>
+        <v>-0.3378993240909592</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1582</v>
+        <v>1217</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>192.0535719787309</v>
+        <v>192.9307045529359</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>44.13305888586285</v>
+        <v>29.31252516957822</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13.70675874869836</v>
+        <v>22.01298880478296</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.947212138697004</v>
+        <v>1.360898114894205</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0177087853551264</v>
+        <v>-0.01691312566274495</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1536</v>
+        <v>1444</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>191.9234449213297</v>
+        <v>191.4544002663449</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>43.8</v>
+        <v>6.66</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>31.78735336205506</v>
+        <v>38.32101732290195</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>24.10910217417911</v>
+        <v>21.88645094564079</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.8609879271902744</v>
+        <v>1.001584990708859</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.08278394494096231</v>
+        <v>-0.01417395940755704</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1220</v>
+        <v>1531</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>187.5397055736768</v>
+        <v>189.2001115483711</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>38.27339319066832</v>
+        <v>40.21898436341603</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>18.31161579458778</v>
+        <v>19.15769520255517</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.6835417548362436</v>
+        <v>0.1910303369452782</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0151198826437181</v>
+        <v>0.01499404686367239</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1527</v>
+        <v>1521</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>179.3729286086377</v>
+        <v>184.53663451125</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>32.05</v>
+        <v>25</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>37.17682644029292</v>
+        <v>39.89574361894764</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>10.0856466835269</v>
+        <v>22.60886461612286</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.7015852638147142</v>
+        <v>0.5399184266849736</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0379584621173449</v>
+        <v>-0.09427439949499988</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1529</v>
+        <v>1447</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>176.399838087042</v>
+        <v>182.9010162276014</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>14.7</v>
+        <v>6.22</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>35.60669369247269</v>
+        <v>37.36424643908072</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>21.45247894348248</v>
+        <v>23.51100450974235</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.3759249138092665</v>
+        <v>1.122346288879889</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0352602751116273</v>
+        <v>-0.01097314849241471</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1338</v>
+        <v>1231</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>175.6494101686914</v>
+        <v>181.8618183480429</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>14.45</v>
+        <v>74.3</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>41.53060190059864</v>
+        <v>20.77512246992806</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>24.7414287256596</v>
+        <v>36.12172669326548</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.4976793908482957</v>
+        <v>0.7811844471055056</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0586062973501558</v>
+        <v>-0.306433995964742</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1436</v>
+        <v>1454</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>165.1629217276463</v>
+        <v>172.6220656043152</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>35.2</v>
+        <v>12</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>36.68310712507354</v>
+        <v>40.41731726077874</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13.32351286118777</v>
+        <v>20.99784951340072</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.8476287377514268</v>
+        <v>0.9062851370223991</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0187665460196279</v>
+        <v>-0.05279314742536149</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1446</v>
+        <v>1538</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>161.513198407225</v>
+        <v>170.2109922092429</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>39.13823099058795</v>
+        <v>38.74514950152395</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>12.03879513761714</v>
+        <v>17.09814371727719</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.036579126426111</v>
+        <v>0.1507890554741108</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0017627701093208</v>
+        <v>-1.040451370784145</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>150.4639235773381</v>
+        <v>159.8815429873118</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>21.55</v>
+        <v>20.2</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>47.08398964037266</v>
+        <v>50.06999577437925</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>7.494613853884655</v>
+        <v>5.946343943890253</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.7250902417192936</v>
+        <v>0.5098654521723434</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0099105353634309</v>
+        <v>0.2266480968154221</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1530</v>
+        <v>1471</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>146.9065934013783</v>
+        <v>158.3932473135707</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>26.5</v>
+        <v>9.01</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>42.86656467133166</v>
+        <v>32.40390741238264</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>17.29023226135435</v>
+        <v>15.84219308720742</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.4184158987861103</v>
+        <v>1.381537630934448</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0135298723187785</v>
+        <v>-0.02329689748786888</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1227</v>
+        <v>1466</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>144.3903758517655</v>
+        <v>157.5768665362972</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>27.6</v>
+        <v>14.4</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>37.83218394319611</v>
+        <v>43.58614453866051</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17.8064332104177</v>
+        <v>15.99865271575751</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.7334442338185182</v>
+        <v>0.7138346245074088</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0093658289653831</v>
+        <v>0.04832510580186766</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1341</v>
+        <v>1452</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>143.8381140672819</v>
+        <v>150.1238547808779</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>0</v>
+        <v>10.65</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>37.10901102721344</v>
+        <v>42.95216515094675</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>8.465557723104386</v>
+        <v>15.94059430660055</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.0139395488232697</v>
+        <v>0.3061135049663243</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-2.825112366909788</v>
+        <v>0.02715903383953844</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1531</v>
+        <v>1540</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>134.2001115483711</v>
+        <v>139.4856444413946</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>11.4</v>
+        <v>18.65</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>40.21898441447984</v>
+        <v>38.71151270596647</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>19.15769520255517</v>
+        <v>10.45389297204655</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.1910303369452781</v>
+        <v>0.6394762684124387</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0149940468516551</v>
+        <v>-0.002725307163337021</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1432</v>
+        <v>1417</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>115.8215544552968</v>
+        <v>139.4479191146526</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>14.9</v>
+        <v>8.09</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>36.44424975773609</v>
+        <v>42.24321412130227</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>17.67498878329866</v>
+        <v>13.37833833198464</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.5843450739975848</v>
+        <v>0.4283024881512028</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0075459469368372</v>
+        <v>0.003163794731219943</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1471</v>
+        <v>1441</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>103.3932473135692</v>
+        <v>139.3426903358456</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>32.40390741238264</v>
+        <v>8.101614096073149</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>15.84219314779075</v>
+        <v>32.2621861209558</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.381537630934448</v>
+        <v>0.08126407941833376</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0232968974758521</v>
+        <v>-0.632821361759434</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1452</v>
+        <v>1218</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>95.12385478087792</v>
+        <v>137.2897255083023</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>10.65</v>
+        <v>14.25</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>42.95216517971027</v>
+        <v>44.76535376608174</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>15.94059368121415</v>
+        <v>6.053047155210829</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.3061135049663243</v>
+        <v>0.8043434055369213</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.0271590336953305</v>
+        <v>-0.02149349948105486</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1540</v>
+        <v>1529</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>84.48564444139456</v>
+        <v>136.399838087042</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>18.65</v>
+        <v>14.7</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>38.71151263362463</v>
+        <v>35.60669345096761</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>10.45389300167756</v>
+        <v>21.45247890136554</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.6394762684124387</v>
+        <v>0.3759249138092666</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0027253069109748</v>
+        <v>-0.03526027506355722</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1417</v>
+        <v>1436</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>84.44791911465255</v>
+        <v>105.1629217276463</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>8.09</v>
+        <v>35.2</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>42.24321407234041</v>
+        <v>36.68310695845339</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>13.37833830948702</v>
+        <v>13.32351286118778</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.4283024881512027</v>
+        <v>0.8476287377514268</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.0031637947432374</v>
+        <v>-0.01876654601962796</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1435</v>
+        <v>1530</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>79.88154298731179</v>
+        <v>86.90659340137803</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>20.2</v>
+        <v>26.5</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>50.06999589013028</v>
+        <v>42.86656463493487</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>5.946343787000083</v>
+        <v>17.2902323064675</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.5098654521723434</v>
+        <v>0.4184158987861103</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.2266480993029433</v>
+        <v>0.0135298723067625</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>1466</v>
+        <v>1227</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>77.57686653629737</v>
+        <v>84.39037585176544</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>14.4</v>
+        <v>27.6</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>43.58614458150807</v>
+        <v>37.83218395728447</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>15.99865271575751</v>
+        <v>17.80643324171685</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.7138346245074088</v>
+        <v>0.7334442338185182</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.0483251058138852</v>
+        <v>-0.009365828989417624</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>1219</v>
+        <v>1341</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>54.46738892973687</v>
+        <v>83.83811406728185</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>46.32820849766966</v>
+        <v>37.10901102618477</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>13.43046745873234</v>
+        <v>8.465557671708474</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.4522391118085424</v>
+        <v>0.01393954882326975</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>0</v>
@@ -7513,11 +7513,11 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.0043065105761719</v>
+        <v>-2.825112366861719</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq1_2026-10-22.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-22.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>67.22819401833083</v>
+        <v>67.22819398842594</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>50.98827078081172</v>
+        <v>50.98827085050917</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.885756429607231</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1247669717314016</v>
+        <v>0.1247669717054427</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>74.65694148261387</v>
+        <v>74.65694168122968</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>35.20061183568823</v>
+        <v>35.20061196990339</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.509864838249063</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.178410070576341</v>
+        <v>0.1784100703946423</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.50565610259397</v>
+        <v>67.5056561594111</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>40.84737949354994</v>
+        <v>40.84737971132715</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.697540842941109</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.03878559625934105</v>
+        <v>0.03878559623338287</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>66.83291417447336</v>
+        <v>66.83291422716002</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>26.83188236739417</v>
+        <v>26.83188239631996</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0.8012040686294437</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>75.90264241624436</v>
+        <v>75.90264246993375</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>67.32218148872418</v>
+        <v>67.32218159404157</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2.675067735922812</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.7106369435236903</v>
+        <v>0.7106369429785833</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>881.1465846849743</v>
+        <v>881.1465846849742</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>25.9</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>61.21968079438652</v>
+        <v>61.21968084120295</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>31.86824647567126</v>
+        <v>31.86824649174469</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>4.318140680598007</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.01683316871074081</v>
+        <v>-0.0168331688535106</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>64.64530955491284</v>
+        <v>64.64530960569995</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.88550414344115</v>
+        <v>22.88550418193258</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>5.107305877482982</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2264940050308146</v>
+        <v>0.2264940049918794</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>72.81261402898284</v>
+        <v>72.81261398142284</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>16.81551510010856</v>
+        <v>16.81551512012239</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>5.434070040980663</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.5360087806822283</v>
+        <v>0.5360087807028222</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>67.02608781183133</v>
+        <v>67.02608797022444</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>50.93368224852669</v>
+        <v>50.93368260422874</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.134148269745486</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.0452511197424359</v>
+        <v>-0.04525112026158373</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>75.48451859660825</v>
+        <v>75.48451856138273</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>44.7818591829032</v>
+        <v>44.78185920319464</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>0.7015148824678775</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>58.68973236823521</v>
+        <v>58.68973244246511</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22.52493958528356</v>
+        <v>22.52493966124407</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.899879554683425</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.03134056231947421</v>
+        <v>-0.03134056241032546</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.94408705260311</v>
+        <v>63.94408716312676</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>33.41179717905271</v>
+        <v>33.41179720512135</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.6783956063873652</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.147858199281586</v>
+        <v>1.147858198892192</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>66.41068528399984</v>
+        <v>66.41068530488567</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>37.8620539103713</v>
+        <v>37.86205394942604</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0.4762559980374482</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>4.134197855375534</v>
+        <v>4.134197855115971</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>50.31850582068898</v>
+        <v>50.31850578639637</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>34.34935146180015</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.4444131549050043</v>
+        <v>-0.4444131548530863</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.1484781941305</v>
+        <v>56.14847813983678</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20.49943886509741</v>
+        <v>20.49943875578506</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0.6430549803829058</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.03910150812958971</v>
+        <v>0.0391015081815056</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>48.88576558020389</v>
+        <v>48.88576560429723</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>23.53005489333985</v>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>625.3482834581496</v>
+        <v>625.3482834581494</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>14.55</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.92073618613777</v>
+        <v>54.92073615385726</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>16.6983919890933</v>
+        <v>16.69839206628611</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.5315720086149386</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>620.29575185482</v>
+        <v>620.2957518548201</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>13.9</v>
@@ -1456,7 +1456,7 @@
         <v>52.57465550717582</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21.89920479298087</v>
+        <v>21.89920482240279</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.3663848025068586</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.01318895398077691</v>
+        <v>-0.01318895399375591</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>56.56586679743685</v>
+        <v>56.56586678628602</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>43.51910231715581</v>
+        <v>43.51910239281162</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1.052114640484283</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-1.577043196913085</v>
+        <v>-1.577043197094817</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>54.51453730355608</v>
+        <v>54.51453742783769</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>19.9678902238398</v>
+        <v>19.96789041810956</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.9038954883700848</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.02756989543045099</v>
+        <v>0.02756989530065895</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>44.19179884816317</v>
+        <v>44.19179891154599</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>31.8314960356828</v>
+        <v>31.83149605483471</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.186265452776034</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.01087099059645795</v>
+        <v>0.01087099060943742</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>47.16151897971363</v>
+        <v>47.16151896894623</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>41.36980284747396</v>
+        <v>41.36980294127662</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.4620147805487044</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.1796110411469446</v>
+        <v>-0.1796110411495419</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>64.61188617286926</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>29.49881619415126</v>
+        <v>29.49881620630818</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.8017099990846154</v>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>52.15532288858483</v>
+        <v>52.15532367404824</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>12.11643028644397</v>
+        <v>12.1164318243229</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.2489099817051164</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.07544777278270004</v>
+        <v>0.07544776766909794</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>47.28923752711714</v>
+        <v>47.28923757597592</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>39.49940665830184</v>
+        <v>39.49940682742422</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.5643919099444266</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.9097498069136005</v>
+        <v>-0.909749807158271</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>545.7225723372153</v>
+        <v>545.7225723372154</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>73.8</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>51.61101266922207</v>
+        <v>51.61101265319471</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>38.3520491998043</v>
+        <v>38.35204925791102</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.6013248262975751</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.5021899417599913</v>
+        <v>-0.5021899417989282</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>535.7105702311541</v>
+        <v>535.7105702311542</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>43.15</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>48.43272904964675</v>
+        <v>48.43272907025969</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>10.0096741267398</v>
+        <v>10.0096741684959</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.9006456250374378</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.01340311611296929</v>
+        <v>0.01340311608700734</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.80010973807624</v>
+        <v>51.80010964121629</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45.89465837480962</v>
+        <v>45.89465848349738</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.5490835262969375</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.04145491806589163</v>
+        <v>-0.04145491802955109</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>55.1794265490582</v>
+        <v>55.1794262083976</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>26.34376177058579</v>
+        <v>26.34376179738685</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.4785622234440209</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1284552826026084</v>
+        <v>0.1284552829919584</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>54.47681658305314</v>
+        <v>54.47681661908713</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>37.83509269077872</v>
+        <v>37.83509276485403</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.5334352961232455</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.01415644551058193</v>
+        <v>0.01415644547164779</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>55.11004129299651</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23.35014564415632</v>
+        <v>23.35014579607236</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.8490513455903952</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.2353773387000584</v>
+        <v>-0.2353773390115483</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>517.5159755642122</v>
+        <v>517.5159755642121</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>846</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>42.08095388467736</v>
+        <v>42.08095386568425</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>31.95696279954685</v>
+        <v>31.9569628647352</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.8192230758207769</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-25.0275619679547</v>
+        <v>-25.02756196951225</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>43.43331045476441</v>
+        <v>43.43331054955119</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>23.18524993762747</v>
+        <v>23.1852499836581</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.5782598888956022</v>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>41.03846279133447</v>
+        <v>41.03846305375814</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>13.76842119257366</v>
+        <v>13.76842122587007</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>3.710012438565919</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.02153990639402967</v>
+        <v>-0.02153990643296569</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>38.6869199916101</v>
+        <v>38.68692009798401</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11.42811229698812</v>
+        <v>11.4281123547563</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.6214000071743462</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.8305585320714264</v>
+        <v>-0.8305585337586323</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>480.930952705536</v>
+        <v>480.9309527055358</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>21.75</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>43.03933676744486</v>
+        <v>43.03933682502424</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>21.01873653586321</v>
+        <v>21.0187365789877</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.7439184876399714</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0154379133416423</v>
+        <v>0.01543791328972619</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>43.31295781375929</v>
+        <v>43.31295776200458</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>37.7831434588695</v>
+        <v>37.78314352969066</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.5280489279729099</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.0825021932778363</v>
+        <v>-0.08250219329081446</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>47.63970805635945</v>
+        <v>47.63970803071238</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>24.46382271990138</v>
+        <v>24.46382276920145</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.4005305714480796</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0994551885893783</v>
+        <v>-0.09945518862831493</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>461.2596177740492</v>
+        <v>461.2596177740485</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>20</v>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>50.53173033559301</v>
+        <v>50.53173034343114</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>10.6238493478604</v>
+        <v>10.62384955175526</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>2.851818566293085</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.07044048162124739</v>
+        <v>0.07044048147848354</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45.90484693019192</v>
+        <v>45.90484707074836</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16.09166015874677</v>
+        <v>16.09166021232069</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.9830428177862458</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.02387868821441951</v>
+        <v>0.02387868795486116</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>47.91113729098156</v>
+        <v>47.91113739662757</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>20.7706201131799</v>
+        <v>20.77062009857078</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>1.046944844780225</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2491873195380336</v>
+        <v>0.2491873192784642</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45.52996769037252</v>
+        <v>45.52996767493394</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>28.72846170757203</v>
+        <v>28.72846159659593</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.5969970290769615</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.07895135550931476</v>
+        <v>-0.07895135549633486</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>53.48868763967705</v>
+        <v>53.48868767907326</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>17.83851628019204</v>
+        <v>17.83851637131479</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.94351239308079</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.01672001997694503</v>
+        <v>0.01672001995098953</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.90119524052107</v>
+        <v>48.90119524669444</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.21305720695588</v>
+        <v>15.21305716388626</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.9174516046541222</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.07487907053995242</v>
+        <v>-0.07487907074761091</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>40.5662988135626</v>
+        <v>40.56629876217429</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>31.68460792312481</v>
+        <v>31.6846080064185</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.7366654226485709</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1081335552827524</v>
+        <v>-0.1081335552697738</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>58.47485539775608</v>
+        <v>58.47485537756555</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>64.22641136979226</v>
+        <v>64.22641151136584</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.1763728741855054</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.61039192268831</v>
+        <v>51.61039199843174</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13.1423371512287</v>
+        <v>13.14233716754401</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.5422154285748083</v>
@@ -3046,7 +3046,7 @@
         <v>48.07826756401787</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.37057198700673</v>
+        <v>13.37057198700672</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.3545110359982702</v>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>426.2256036612502</v>
+        <v>426.2256036612503</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>26.5</v>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.37519985326762</v>
+        <v>48.37519996138513</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>13.52240630057613</v>
+        <v>13.52240632268671</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>1.036533289575128</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.08582274837837976</v>
+        <v>0.08582274819667798</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46.66568627613604</v>
+        <v>46.66568635272273</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>29.72973539784932</v>
+        <v>29.72973555512544</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.2241673381767101</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.1746697746732524</v>
+        <v>-0.1746697747641023</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>43.7304750753824</v>
+        <v>43.73047503588652</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>34.41011017552491</v>
+        <v>34.410110244324</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.5287290176459353</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.09724607069696029</v>
+        <v>-0.09724607070993924</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.62412261036246</v>
+        <v>52.6241226032864</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>6.444766285013309</v>
+        <v>6.444766288243534</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.4875341668806329</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.2529556236433477</v>
+        <v>-0.2529556235914483</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>47.43459299079519</v>
+        <v>47.4345929121767</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>36.48648910387239</v>
+        <v>36.48648929627024</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.4503480288655173</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.05008545236776255</v>
+        <v>-0.05008545235478354</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>53.39231253641537</v>
+        <v>53.39231258147935</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>17.52592621661223</v>
+        <v>17.52592628712955</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>1.110544920475465</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.01060223128731803</v>
+        <v>0.01060223122242689</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>399.3025367340296</v>
+        <v>399.3025367340298</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>10.3</v>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>43.39820073397857</v>
+        <v>43.39820066028695</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>23.09991949363018</v>
+        <v>23.09991959203426</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1.690104392507155</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.02316421767544768</v>
+        <v>0.02316421768842664</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>39.32029416923925</v>
+        <v>39.32029422982587</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>44.38443207812463</v>
+        <v>44.38443212941924</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.26527737954334</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.03832927483297471</v>
+        <v>0.03832927484595461</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.47628258805543</v>
+        <v>51.47628324819883</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>9.195139657620912</v>
+        <v>9.195140867425428</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>1.213837046724031</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.06219018997165694</v>
+        <v>-0.06219019325526491</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>388.7671418522369</v>
+        <v>388.7671418522368</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>18.85</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>34.97952203631272</v>
+        <v>34.97952221959444</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>44.88680352163931</v>
+        <v>44.88680352530255</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>1.444803384559349</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0007838578730914036</v>
+        <v>-0.0007838579898996334</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>384.4145656427831</v>
+        <v>384.4145656427888</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>98.59999999999999</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>40.93268048618865</v>
+        <v>40.93268069948992</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11.74183229638204</v>
+        <v>11.74183240172536</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.7215689761067196</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.4176754123772879</v>
+        <v>-0.417675413804938</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>51.10893499769771</v>
+        <v>51.10893496109806</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>19.23056757529915</v>
+        <v>19.23056751969887</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>1.107740551194117</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.008362932128092672</v>
+        <v>0.008362932024265073</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>379.0206616479385</v>
+        <v>379.0206616479383</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>31</v>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>49.60348735734944</v>
+        <v>49.60348738275516</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>11.84462246610018</v>
+        <v>11.84462254659206</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>1.268534588509361</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.03824517284626756</v>
+        <v>-0.0382451729630765</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>375.7268237757937</v>
+        <v>375.7268237757938</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>17</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>43.05829126220716</v>
+        <v>43.05829138163871</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.8267462131565</v>
+        <v>12.82674628956885</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.4001182870078424</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.003922198414267282</v>
+        <v>0.003922198388312065</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>42.37011668304041</v>
+        <v>42.3701167487967</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>8.319428195744438</v>
+        <v>8.319427966574546</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.4600557741757824</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.2191739783363484</v>
+        <v>0.2191739813214595</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>50.73405679072533</v>
+        <v>50.73405691926826</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>7.973975386292214</v>
+        <v>7.973975423213428</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.5975139833209947</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0004004809074422515</v>
+        <v>0.0004004808814840428</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>44.89434108506562</v>
+        <v>44.89434105419756</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>34.77860012191497</v>
+        <v>34.7786001449895</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.5454585161494226</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0738363473651118</v>
+        <v>-0.07383634735732553</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>346.6733874472961</v>
+        <v>346.6733874472962</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>26.65</v>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>49.59765327557657</v>
+        <v>49.5976532914535</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>28.4395936734038</v>
+        <v>28.43959363612493</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.5393660494386591</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.05352941674292044</v>
+        <v>0.05352941662611273</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.43472543376139</v>
+        <v>44.43472540499618</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16.63724608769352</v>
+        <v>16.63724609672827</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>3.841408098733572</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.004043074459428808</v>
+        <v>-0.004043074446452521</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>54.76490306619252</v>
+        <v>54.76490287283215</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>8.820709995351043</v>
+        <v>8.820709964488103</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.3444450285100885</v>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>30.27544526690903</v>
+        <v>30.2754452998782</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>28.26196199971221</v>
+        <v>28.26196207568031</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.7234782411867646</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.005899539086103342</v>
+        <v>0.005899539078315641</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>43.36351037534183</v>
+        <v>43.36351028964666</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>16.19488793105122</v>
+        <v>16.19488793326233</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.808491582247074</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.02617305415082732</v>
+        <v>-0.02617305409891257</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>41.1051390941152</v>
+        <v>41.10513916883784</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>27.25126430947455</v>
+        <v>27.25126446151379</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.9228546604900439</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.01251598976722607</v>
+        <v>-0.01251598993595038</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>41.64187541071813</v>
+        <v>41.64187539323201</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.9029000964332</v>
+        <v>15.90290027438911</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.4808313018780662</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.01251024861584429</v>
+        <v>-0.01251024861324925</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>37.30382887658166</v>
+        <v>37.30382884942652</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.48436564886853</v>
+        <v>14.48436563941315</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>1.663891804908274</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.06593604110046239</v>
+        <v>-0.06593604117833188</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>47.80496242511996</v>
+        <v>47.80496237772534</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>32.49655271958042</v>
+        <v>32.49655268292496</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.407632821778858</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.04664076744104809</v>
+        <v>-0.04664076745402679</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>33.01850191987452</v>
+        <v>33.01850203109586</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>30.00260833514157</v>
+        <v>30.00260844242966</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>1.097233452453498</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.06424678548464469</v>
+        <v>-0.06424678573124165</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45.35651936976606</v>
+        <v>45.35651942139969</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>33.07498640195481</v>
+        <v>33.07498638671085</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.3913103384926285</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.04513001617764176</v>
+        <v>-0.04513001619581303</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>38.48702343291328</v>
+        <v>38.48702325705609</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7.617536348053889</v>
+        <v>7.617536382793276</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.6271837785975587</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.009527175774447116</v>
+        <v>0.00952717578742529</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>34.86981328212447</v>
+        <v>34.86981319594247</v>
       </c>
       <c r="I79" s="2" t="n">
         <v>25.36638529354557</v>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>34.23089086729462</v>
+        <v>34.23088979970008</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>18.41097726197723</v>
+        <v>18.41097811400233</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.7588313416947114</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.006374188734929884</v>
+        <v>0.00637418885173828</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>47.12656667669876</v>
+        <v>47.12656670682107</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>14.17372294326239</v>
+        <v>14.17372298714401</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.9979275133066693</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.003183945421184692</v>
+        <v>0.003183945382247713</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>38.48273909190718</v>
+        <v>38.48273887761444</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7.946364096848186</v>
+        <v>7.9463645255898</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>1.141736795086661</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.02105877539483614</v>
+        <v>0.02105877570632486</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>50.37570354983596</v>
+        <v>50.37570355650195</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>8.071739521147883</v>
+        <v>8.071739603631645</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>1.591717518967429</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.273757593606871</v>
+        <v>0.2737575935030396</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>34.63655180391633</v>
+        <v>34.63655212079985</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.61785347832587</v>
+        <v>13.61785360486242</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>1.992951684169262</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.07171242524689847</v>
+        <v>-0.07171242537668543</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>35.74218418674596</v>
+        <v>35.74218414138525</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11.12301220062339</v>
+        <v>11.12301228248422</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>1.760919502465495</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.01614659393983846</v>
+        <v>-0.01614659393724376</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>280.8215544552968</v>
+        <v>280.8215544552973</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>14.9</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>36.44424957313118</v>
+        <v>36.44424994528642</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.67498874108724</v>
+        <v>17.67498879254004</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.5843450739975848</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.007545946936837265</v>
+        <v>-0.007545946962794772</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>48.55393283862234</v>
+        <v>48.55393282858574</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>19.11615589845732</v>
+        <v>19.11615594113584</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.2529138567877762</v>
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>278.5477045692471</v>
+        <v>278.5477045692472</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>13.05</v>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>36.26359413417264</v>
+        <v>36.26359385099953</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>36.43133900512838</v>
+        <v>36.43134016052537</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>1.110804882276412</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.007032436208796455</v>
+        <v>-0.007032436169860101</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>275.80856825208</v>
+        <v>275.8085682520794</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>9.859999999999999</v>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>40.88061474972265</v>
+        <v>40.88061330824178</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>19.32283006700711</v>
+        <v>19.32283039697867</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.9656777798966892</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.002733308688644874</v>
+        <v>-0.002733308623751617</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>272.1628941739328</v>
+        <v>272.1628941739327</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>17.35</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.43434984029913</v>
+        <v>43.43435007362613</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>16.82255517268307</v>
+        <v>16.82255521365153</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>1.169022783709383</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.04150184483052016</v>
+        <v>0.04150184485276265</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>30.25948870534828</v>
+        <v>30.2594886590818</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>34.58904658987375</v>
+        <v>34.58904658087221</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0.6038300506478742</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>48.73350234500433</v>
+        <v>48.73350263634344</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.06062427980989</v>
+        <v>12.06062426556887</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.2324904627064758</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0004678325356735243</v>
+        <v>0.0004678324837585519</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>269.6913430748821</v>
+        <v>269.691343074882</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>15.3</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>35.73061798298103</v>
+        <v>35.73061809196055</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>30.35315962862844</v>
+        <v>30.35315976877381</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>1.253583202524372</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.02073921303832876</v>
+        <v>-0.02073921310322206</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>40.22978147575908</v>
+        <v>40.2297815087816</v>
       </c>
       <c r="I94" s="2" t="n">
         <v>40.17210484007352</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.02320298581588753</v>
+        <v>0.0232029858029085</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>255.6636975973335</v>
+        <v>255.6636975973329</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>63.5</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>37.04555230374353</v>
+        <v>37.04555218429955</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.17341360682296</v>
+        <v>15.17341359534782</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.3550157074723045</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.2656956510363521</v>
+        <v>-0.2656956509584859</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>50.99084933536099</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.7977472693179</v>
+        <v>13.79774724240975</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>1.009326928468627</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.3789605355343183</v>
+        <v>0.3789605355213391</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>247.0535719787309</v>
+        <v>247.0535719787305</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>69.90000000000001</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.13305884213477</v>
+        <v>44.13305890940874</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.70675871013541</v>
+        <v>13.70675867097003</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>1.947212138697003</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.01770878511476737</v>
+        <v>0.01770878467349235</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>31.78735351417725</v>
+        <v>31.78735427169219</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>24.10910253017152</v>
+        <v>24.10910258687021</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.8609879271902744</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0827839458783165</v>
+        <v>-0.08278394642341602</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.32820835490458</v>
+        <v>46.32820850865157</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.4304674303655</v>
+        <v>13.43046753543922</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.4522391118085424</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.00430651056415611</v>
+        <v>-0.004306510590113166</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>38.27339323710818</v>
+        <v>38.27339308707172</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.31161572055116</v>
+        <v>18.31161572625699</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.6835417548362436</v>
@@ -5785,7 +5785,7 @@
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>234.3729286086376</v>
+        <v>234.3729286086362</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>32.05</v>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>37.1768262506079</v>
+        <v>37.17682643631351</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10.08564669800517</v>
+        <v>10.08564701099007</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.7015852638147142</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.03795846211734499</v>
+        <v>-0.03795846226011274</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>232.7062305274775</v>
+        <v>232.7062305274769</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>96.7</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>31.06818699288814</v>
+        <v>31.06818707941413</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.6804090335585</v>
+        <v>18.68040907923018</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>1.711676728001756</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.3157175432616578</v>
+        <v>-0.3157175437548441</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>231.6225511311858</v>
+        <v>231.6225511311849</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>615</v>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>33.3021436707953</v>
+        <v>33.30214368564765</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.71618485340681</v>
+        <v>12.71618488121825</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.5237464880521181</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-7.221732680277878</v>
+        <v>-7.221732687026851</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.53060149759695</v>
+        <v>41.53060187775376</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>24.7414287256596</v>
+        <v>24.7414289684885</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.4976793908482958</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.05860629733813769</v>
+        <v>-0.05860629757175465</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>51.30613010717237</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>8.699330794350457</v>
+        <v>8.699330880273015</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>1.534455435045157</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>38.00230958774962</v>
+        <v>38.00230946826648</v>
       </c>
       <c r="I106" s="2" t="n">
         <v>17.1794584639681</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.003937246013506521</v>
+        <v>0.003937246065421091</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>42.23756923185449</v>
+        <v>42.23756932353022</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.796564228807661</v>
+        <v>9.796564315084856</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.8919521866451359</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.6151077118624446</v>
+        <v>-0.6151077143283727</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>216.5131984072283</v>
+        <v>216.5131984072286</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>13.3</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>39.13823099058795</v>
+        <v>39.13823110943726</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.03879514806371</v>
+        <v>12.03879517598908</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>1.036579126426111</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.001762770061251223</v>
+        <v>0.001762770009335432</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.08398958909182</v>
+        <v>47.08398949244717</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>7.494613851272913</v>
+        <v>7.494613851280223</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.7250902417192936</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.009910535291324934</v>
+        <v>0.009910535161537462</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>201.2126428627774</v>
+        <v>201.2126428627769</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>26</v>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>35.17635308601176</v>
+        <v>35.17635284514378</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>31.24519957971321</v>
+        <v>31.24519962925976</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.3988081913507854</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.009387731286727874</v>
+        <v>0.00938773146843086</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>194.9523194066126</v>
+        <v>194.9523194066122</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>39.95</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>43.65617295722609</v>
+        <v>43.65617313912831</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.56211267146425</v>
+        <v>17.56211252246812</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.5312389084996308</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.01970664848514056</v>
+        <v>0.01970664813471337</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>193.7034867605874</v>
+        <v>193.7034867605876</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>28.9</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>38.25111979138109</v>
+        <v>38.251120029319</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>22.97816376004682</v>
+        <v>22.97816382511045</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.5314132171035814</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.3378993240909592</v>
+        <v>-0.3378993239871319</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>192.9307045529359</v>
+        <v>192.9307045529357</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>9.710000000000001</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.01691312566274495</v>
+        <v>-0.01691312567572451</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>38.32101732290195</v>
+        <v>38.3210174005151</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>21.88645094564079</v>
+        <v>21.88645097900668</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>1.001584990708859</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.01417395940755704</v>
+        <v>-0.01417395944130147</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>40.21898436341603</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>19.15769520255517</v>
+        <v>19.15769523305918</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.1910303369452782</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.01499404686367239</v>
+        <v>0.01499404685069336</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>39.89574361894764</v>
+        <v>39.8957435396395</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>22.60886461612286</v>
+        <v>22.60886457362271</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.5399184266849736</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.09427439949499988</v>
+        <v>-0.0942743995079792</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>182.9010162276014</v>
+        <v>182.901016227601</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>6.22</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>37.36424643908072</v>
+        <v>37.36424647422256</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>23.51100450974235</v>
+        <v>23.51100455219949</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>1.122346288879889</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.01097314849241471</v>
+        <v>-0.01097314850539313</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>181.8618183480429</v>
+        <v>181.8618183480426</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>74.3</v>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>20.77512246992806</v>
+        <v>20.77512345552299</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>36.12172669326548</v>
+        <v>36.12172657205576</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.7811844471055056</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.306433995964742</v>
+        <v>-0.3064339964838934</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>172.6220656043152</v>
+        <v>172.622065604318</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>12</v>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>40.41731726077874</v>
+        <v>40.41731719505214</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>20.99784951340072</v>
+        <v>20.99784949065089</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.9062851370223991</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.05279314742536149</v>
+        <v>-0.05279314737344756</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>38.74514950152395</v>
+        <v>38.74514951413121</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17.09814371727719</v>
+        <v>17.09814368084951</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.1507890554741108</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-1.040451370784145</v>
+        <v>-1.040451370874996</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>159.8815429873118</v>
+        <v>159.8815429873115</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>20.2</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>50.06999577437925</v>
+        <v>50.06999611718037</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>5.946343943890253</v>
+        <v>5.946345208951548</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.5098654521723434</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.2266480968154221</v>
+        <v>0.2266480925937485</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>158.3932473135707</v>
+        <v>158.39324731357</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>9.01</v>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>32.40390741238264</v>
+        <v>32.40390734905704</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>15.84219308720742</v>
+        <v>15.84219300251613</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>1.381537630934448</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.02329689748786888</v>
+        <v>-0.02329689750084775</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>43.58614453866051</v>
+        <v>43.58614458480404</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>15.99865271575751</v>
+        <v>15.99865273214649</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.7138346245074088</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.04832510580186766</v>
+        <v>0.04832510574995136</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>42.95216515094675</v>
+        <v>42.95216474024279</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.94059430660055</v>
+        <v>15.94059467302017</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.3061135049663243</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.02715903383953844</v>
+        <v>0.02715903398230293</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>139.4856444413946</v>
+        <v>139.4856444413938</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>18.65</v>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>38.71151270596647</v>
+        <v>38.71151293968626</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>10.45389297204655</v>
+        <v>10.4538930990547</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.6394762684124387</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.002725307163337021</v>
+        <v>-0.002725307383973807</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>42.24321412130227</v>
+        <v>42.24321417403042</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>13.37833833198464</v>
+        <v>13.37833829015054</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.4283024881512028</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.003163794731219943</v>
+        <v>0.003163794723434196</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>139.3426903358456</v>
+        <v>139.3426903358455</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>0</v>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>8.101614096073149</v>
+        <v>8.101614084452024</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>32.2621861209558</v>
+        <v>32.26218604406749</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.08126407941833376</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.632821361759434</v>
+        <v>-0.6328213617388382</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>44.76535376608174</v>
+        <v>44.76535378377109</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>6.053047155210829</v>
+        <v>6.053047195481095</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.8043434055369213</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.02149349948105486</v>
+        <v>-0.02149349949403238</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>35.60669345096761</v>
+        <v>35.60669350462861</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>21.45247890136554</v>
+        <v>21.45247887624866</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.3759249138092666</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.03526027506355722</v>
+        <v>-0.0352602752841959</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>105.1629217276463</v>
+        <v>105.1629217276462</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>35.2</v>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>36.68310695845339</v>
+        <v>36.68310713789047</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>13.32351286118778</v>
+        <v>13.32351274331679</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.8476287377514268</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.01876654601962796</v>
+        <v>-0.01876654633111702</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>42.86656463493487</v>
+        <v>42.86656468197072</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>17.2902323064675</v>
+        <v>17.2902323758677</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.4184158987861103</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.0135298723067625</v>
+        <v>0.01352987222888691</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>84.39037585176544</v>
+        <v>84.39037585176541</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>27.6</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>37.83218395728447</v>
+        <v>37.83218397245656</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>17.80643324171685</v>
+        <v>17.80643321058857</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.7334442338185182</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.009365828989417624</v>
+        <v>-0.009365829002395354</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>83.83811406728185</v>
+        <v>83.83811406728192</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>0</v>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>37.10901102618477</v>
+        <v>37.10901102455061</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>8.465557671708474</v>
+        <v>8.465557602412245</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.01393954882326975</v>

--- a/output/full_scan/batch_seq1_2026-10-22.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-22.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>67.22819398842594</v>
+        <v>67.22819406826662</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>50.98827085050917</v>
+        <v>50.98827114508993</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.885756429607231</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1247669717054427</v>
+        <v>0.1247669716353623</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>74.65694168122968</v>
+        <v>74.65694170885359</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>35.20061196990339</v>
+        <v>35.20061201114412</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.509864838249063</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1784100703946423</v>
+        <v>0.1784100703806283</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.5056561594111</v>
+        <v>67.50565622059881</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>40.84737971132715</v>
+        <v>40.84737976118824</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.697540842941109</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.03878559623338287</v>
+        <v>0.03878559621936713</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>66.83291422716002</v>
+        <v>66.83291412754593</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>26.83188239631996</v>
+        <v>26.83188237953689</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0.8012040686294437</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4582317267078517</v>
+        <v>0.4582317269321299</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>75.90264246993375</v>
+        <v>75.90264252951931</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>67.32218159404157</v>
+        <v>67.32218159008508</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2.675067735922812</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.7106369429785833</v>
+        <v>0.7106369427543093</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>881.1465846849742</v>
+        <v>881.1465846849743</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>25.9</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>61.21968084120295</v>
+        <v>61.21968087208622</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>31.86824649174469</v>
+        <v>31.86824651282204</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>4.318140680598007</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.0168331688535106</v>
+        <v>-0.0168331688955593</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>64.64530960569995</v>
+        <v>64.64530961413328</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.88550418193258</v>
+        <v>22.88550425046362</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>5.107305877482982</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2264940049918794</v>
+        <v>0.2264940050058953</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>72.81261398142284</v>
+        <v>72.81261403264131</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>16.81551512012239</v>
+        <v>16.81551520788351</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>5.434070040980663</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.5360087807028222</v>
+        <v>0.53600878061385</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>67.02608797022444</v>
+        <v>67.02608801513507</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>50.93368260422874</v>
+        <v>50.93368264617315</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.134148269745486</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.04525112026158373</v>
+        <v>-0.04525112034568712</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.09727343412723777</v>
+        <v>0.09727343411322048</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>58.68973244246511</v>
+        <v>58.68973247454434</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22.52493966124407</v>
+        <v>22.52493964712873</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.899879554683425</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.03134056241032546</v>
+        <v>-0.03134056242434258</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.94408716312676</v>
+        <v>63.94408747784205</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>33.41179720512135</v>
+        <v>33.41179713616474</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.6783956063873652</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.147858198892192</v>
+        <v>1.14785819931272</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>66.41068530488567</v>
+        <v>66.41068536176695</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>37.86205394942604</v>
+        <v>37.86205389217329</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0.4762559980374482</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>50.31850578639637</v>
+        <v>50.31850580347449</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>34.34935146180015</v>
+        <v>34.3493513625862</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.5959525816474684</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.4444131548530863</v>
+        <v>-0.4444131551614587</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.14847813983678</v>
+        <v>56.14847807043574</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20.49943875578506</v>
+        <v>20.49943876514065</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0.6430549803829058</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0391015081815056</v>
+        <v>0.03910150819552225</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>48.88576560429723</v>
+        <v>48.88576557835056</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>23.53005489333985</v>
+        <v>23.53005504621703</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.784399689079536</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.01664002015503629</v>
+        <v>-0.01664002014102071</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>625.3482834581494</v>
+        <v>625.3482834581496</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>14.55</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.92073615385726</v>
+        <v>54.92073624568924</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>16.69839206628611</v>
+        <v>16.69839202725624</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.5315720086149386</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.02338600392438938</v>
+        <v>0.02338600391037216</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.57465550717582</v>
+        <v>52.5746555263542</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21.89920482240279</v>
+        <v>21.89920472552367</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.3663848025068586</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.01318895399375591</v>
+        <v>-0.01318895400777273</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>56.56586678628602</v>
+        <v>56.56586679892664</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>43.51910239281162</v>
+        <v>43.5191025502931</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1.052114640484283</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-1.577043197094817</v>
+        <v>-1.577043197823663</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>54.51453742783769</v>
+        <v>54.51453744845245</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>19.96789041810956</v>
+        <v>19.96789044440318</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.9038954883700848</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.02756989530065895</v>
+        <v>0.02756989531468068</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>44.19179891154599</v>
+        <v>44.1917987821331</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>31.83149605483471</v>
+        <v>31.83149610268009</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.186265452776034</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.01087099060943742</v>
+        <v>0.01087099065148765</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>47.16151896894623</v>
+        <v>47.16151896430795</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>41.36980294127662</v>
+        <v>41.36980289120726</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.4620147805487044</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.1796110411495419</v>
+        <v>-0.1796110411803773</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>64.61188617286926</v>
+        <v>64.61188614565484</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>29.49881620630818</v>
+        <v>29.4988162359017</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.8017099990846154</v>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>52.15532367404824</v>
+        <v>52.15532327036512</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>12.1164318243229</v>
+        <v>12.11643055802605</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.2489099817051164</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.07544776766909794</v>
+        <v>0.07544777319178941</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>47.28923757597592</v>
+        <v>47.28923759720881</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>39.49940682742422</v>
+        <v>39.49940680673548</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.5643919099444266</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.909749807158271</v>
+        <v>-0.9097498070381662</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>545.7225723372154</v>
+        <v>545.7225723372153</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>73.8</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>51.61101265319471</v>
+        <v>51.61101266613989</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>38.35204925791102</v>
+        <v>38.35204924639145</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.6013248262975751</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.5021899417989282</v>
+        <v>-0.5021899420091787</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>535.7105702311542</v>
+        <v>535.710570231155</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>43.15</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>48.43272907025969</v>
+        <v>48.43272913894283</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>10.0096741684959</v>
+        <v>10.00967414039615</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.9006456250374378</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.01340311608700734</v>
+        <v>0.01340311611504297</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.80010964121629</v>
+        <v>51.80010966964143</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45.89465848349738</v>
+        <v>45.89465832465102</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.5490835262969375</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.04145491802955109</v>
+        <v>-0.04145491808561985</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>55.1794262083976</v>
+        <v>55.17942632238739</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>26.34376179738685</v>
+        <v>26.34376177125698</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.4785622234440209</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1284552829919584</v>
+        <v>0.128455282431282</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>54.47681661908713</v>
+        <v>54.4768165802813</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>37.83509276485403</v>
+        <v>37.83509284711179</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.5334352961232455</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>55.11004129299651</v>
+        <v>55.1100413764452</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23.35014579607236</v>
+        <v>23.35014599621263</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.8490513455903952</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.2353773390115483</v>
+        <v>-0.2353773393479477</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>42.08095386568425</v>
+        <v>42.08095392126996</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>31.9569628647352</v>
+        <v>31.95696305840941</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.8192230758207769</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-25.02756196951225</v>
+        <v>-25.02756197329683</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>43.43331054955119</v>
+        <v>43.43331039522106</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>23.1852499836581</v>
+        <v>23.18525008313585</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.5782598888956022</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.02834004245045718</v>
+        <v>0.02834004253455696</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>41.03846305375814</v>
+        <v>41.03846319352465</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>13.76842122587007</v>
+        <v>13.76842115646427</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>3.710012438565919</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.02153990643296569</v>
+        <v>-0.02153990634886209</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>495.7151263707709</v>
+        <v>495.7151263707708</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>160</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>38.68692009798401</v>
+        <v>38.68692035179406</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11.4281123547563</v>
+        <v>11.42811246218118</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.6214000071743462</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.8305585337586323</v>
+        <v>-0.8305585345996461</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>43.03933682502424</v>
+        <v>43.03933687304897</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>21.0187365789877</v>
+        <v>21.01873652113024</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.7439184876399714</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.01543791328972619</v>
+        <v>0.01543791327570723</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>43.31295776200458</v>
+        <v>43.31295803084129</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>37.78314352969066</v>
+        <v>37.78314363574849</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.5280489279729099</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.08250219329081446</v>
+        <v>-0.08250219334688401</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>47.63970803071238</v>
+        <v>47.63970813217156</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>24.46382276920145</v>
+        <v>24.46382294520946</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.4005305714480796</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.09945518862831493</v>
+        <v>-0.0994551887264325</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>461.2596177740485</v>
+        <v>461.2596177740491</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>20</v>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>50.53173034343114</v>
+        <v>50.5317303747298</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>10.62384955175526</v>
+        <v>10.6238495746438</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>2.851818566293085</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.07044048147848354</v>
+        <v>0.07044048138036485</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>45.90484707074836</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16.09166021232069</v>
+        <v>16.09166011837508</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.9830428177862458</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.02387868795486116</v>
+        <v>0.02387868809501446</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>47.91113739662757</v>
+        <v>47.91113745847422</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>20.77062009857078</v>
+        <v>20.77062002002396</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>1.046944844780225</v>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45.52996767493394</v>
+        <v>45.5299675748732</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>28.72846159659593</v>
+        <v>28.72846175073957</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.5969970290769615</v>
@@ -2764,7 +2764,7 @@
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>446.1275552542835</v>
+        <v>446.1275552542834</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>11.05</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>53.48868767907326</v>
+        <v>53.48868775839224</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>17.83851637131479</v>
+        <v>17.83851632770369</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.94351239308079</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.01672001995098953</v>
+        <v>0.01672001993697055</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>446.0184672060134</v>
+        <v>446.0184672060135</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>69.7</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.90119524669444</v>
+        <v>48.90119531407304</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.21305716388626</v>
+        <v>15.21305722505362</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.9174516046541222</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.07487907074761091</v>
+        <v>-0.07487907094385104</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>40.56629876217429</v>
+        <v>40.56629877456848</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>31.6846080064185</v>
+        <v>31.68460792062989</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.7366654226485709</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1081335552697738</v>
+        <v>-0.1081335553118239</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>58.47485537756555</v>
+        <v>58.47485541475015</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>64.22641151136584</v>
+        <v>64.2264115584602</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.1763728741855054</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.1436329391723479</v>
+        <v>-0.1436329391963704</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>434.7350949140956</v>
+        <v>434.7350949140958</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>107</v>
@@ -2993,7 +2993,7 @@
         <v>51.61039199843174</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13.14233716754401</v>
+        <v>13.14233712235288</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.5422154285748083</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.2348333998358355</v>
+        <v>0.2348334001161878</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>426.2256036612503</v>
+        <v>426.2256036612502</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>26.5</v>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.37519996138513</v>
+        <v>48.37520002038438</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>13.52240632268671</v>
+        <v>13.52240634674843</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>1.036533289575128</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.08582274819667798</v>
+        <v>0.08582274814061394</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46.66568635272273</v>
+        <v>46.66568631565318</v>
       </c>
       <c r="I51" s="2" t="n">
         <v>29.72973555512544</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.1746697747641023</v>
+        <v>-0.1746697746940243</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>43.73047503588652</v>
+        <v>43.73047507842054</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>34.410110244324</v>
+        <v>34.41011030747746</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.5287290176459353</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.09724607070993924</v>
+        <v>-0.09724607078002473</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>408.0867869331105</v>
+        <v>408.0867869331107</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>88.59999999999999</v>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.6241226032864</v>
+        <v>52.62412263076303</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>6.444766288243534</v>
+        <v>6.444766286668123</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.4875341668806329</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.2529556235914483</v>
+        <v>-0.2529556236475159</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>47.4345929121767</v>
+        <v>47.43459298148233</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>36.48648929627024</v>
+        <v>36.48648926027415</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.4503480288655173</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.05008545235478354</v>
+        <v>-0.05008545242487034</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>53.39231258147935</v>
+        <v>53.39231282372943</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>17.52592628712955</v>
+        <v>17.52592633461374</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>1.110544920475465</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.01060223122242689</v>
+        <v>0.01060223118037502</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>399.3025367340298</v>
+        <v>399.3025367340297</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>10.3</v>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>43.39820066028695</v>
+        <v>43.39820078456646</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>23.09991959203426</v>
+        <v>23.09991960805586</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1.690104392507155</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.02316421768842664</v>
+        <v>0.02316421767441171</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>39.32029422982587</v>
+        <v>39.32029419720229</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>44.38443212941924</v>
+        <v>44.38443221165659</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.26527737954334</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.03832927484595461</v>
+        <v>0.03832927488800508</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>51.47628324819883</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>9.195140867425428</v>
+        <v>9.195140872499589</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>1.213837046724031</v>
@@ -3559,7 +3559,7 @@
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>388.7671418522368</v>
+        <v>388.7671418522366</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>18.85</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>34.97952221959444</v>
+        <v>34.97952300977602</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>44.88680352530255</v>
+        <v>44.88680351426455</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>1.444803384559349</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0007838579898996334</v>
+        <v>-0.0007838580179355403</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>40.93268069948992</v>
+        <v>40.93268067651901</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11.74183240172536</v>
+        <v>11.74183244630981</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.7215689761067196</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.417675413804938</v>
+        <v>-0.4176754139451156</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>51.10893496109806</v>
+        <v>51.10893511875808</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>19.23056751969887</v>
+        <v>19.23056761182529</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>1.107740551194117</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.008362932024265073</v>
+        <v>0.008362931884096678</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>49.60348738275516</v>
+        <v>49.60348749241383</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>11.84462254659206</v>
+        <v>11.84462265383216</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>1.268534588509361</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0382451729630765</v>
+        <v>-0.03824517306119814</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>43.05829138163871</v>
+        <v>43.0582915517282</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.82674628956885</v>
+        <v>12.82674623738915</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.4001182870078424</v>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>42.3701167487967</v>
+        <v>42.37011679600633</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>8.319427966574546</v>
+        <v>8.319427580584225</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.4600557741757824</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.2191739813214595</v>
+        <v>0.2191739849658891</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>50.73405691926826</v>
+        <v>50.7340569466283</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>7.973975423213428</v>
+        <v>7.973975485354818</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.5975139833209947</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0004004808814840428</v>
+        <v>0.0004004809235365874</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>44.89434105419756</v>
+        <v>44.89434106185504</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>34.7786001449895</v>
+        <v>34.77860012876623</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.5454585161494226</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.07383634735732553</v>
+        <v>-0.07383634737134342</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>346.6733874472962</v>
+        <v>346.6733874472952</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>26.65</v>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>49.5976532914535</v>
+        <v>49.59765344561504</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>28.43959363612493</v>
+        <v>28.43959363310234</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.5393660494386591</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.05352941662611273</v>
+        <v>0.05352941651397894</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.43472540499618</v>
+        <v>44.43472579744652</v>
       </c>
       <c r="I68" s="2" t="n">
         <v>16.63724609672827</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.004043074446452521</v>
+        <v>-0.004043074460464507</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>54.76490287283215</v>
+        <v>54.76490311546614</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>8.820709964488103</v>
+        <v>8.820710048050584</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.3444450285100885</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.00996388305984125</v>
+        <v>0.009963882989755608</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>30.2754452998782</v>
+        <v>30.27544535439078</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>28.26196207568031</v>
+        <v>28.26196199651295</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.7234782411867646</v>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>43.36351028964666</v>
+        <v>43.36351032575151</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>16.19488793326233</v>
+        <v>16.19488799147967</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.808491582247074</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.02617305409891257</v>
+        <v>-0.02617305416899768</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>41.10513916883784</v>
+        <v>41.10513923354406</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>27.25126446151379</v>
+        <v>27.25126434418434</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.9228546604900439</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.01251598993595038</v>
+        <v>-0.01251599000603373</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>41.64187539323201</v>
+        <v>41.64187540430454</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.90290027438911</v>
+        <v>15.90290034858677</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.4808313018780662</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.01251024861324925</v>
+        <v>-0.01251024861885455</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>306.8260899314311</v>
+        <v>306.8260899314309</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>25.2</v>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>37.30382884942652</v>
+        <v>37.30382886404852</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.48436563941315</v>
+        <v>14.48436562863219</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>1.663891804908274</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.06593604117833188</v>
+        <v>-0.06593604129046854</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>47.80496237772534</v>
+        <v>47.80496242876569</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>32.49655268292496</v>
+        <v>32.49655268876375</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.407632821778858</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.04664076745402679</v>
+        <v>-0.04664076751009566</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>33.01850203109586</v>
+        <v>33.01850237081086</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>30.00260844242966</v>
+        <v>30.0026085013421</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>1.097233452453498</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.06424678573124165</v>
+        <v>-0.06424678578731008</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45.35651942139969</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>33.07498638671085</v>
+        <v>33.07498639151169</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.3913103384926285</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.04513001619581303</v>
+        <v>-0.04513001617899268</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>38.48702325705609</v>
+        <v>38.48702340001114</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7.617536382793276</v>
+        <v>7.617536367085991</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.6271837785975587</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.00952717578742529</v>
+        <v>0.009527175661270704</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>301.4427551264689</v>
+        <v>301.4427551264691</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>9.859999999999999</v>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>34.86981319594247</v>
+        <v>34.86981328875386</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>25.36638529354557</v>
+        <v>25.36638541816729</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>1.395196716124667</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.000142484817384686</v>
+        <v>0.0001424848033682036</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>34.23088979970008</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>18.41097811400233</v>
+        <v>18.41097809777801</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.7588313416947114</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.00637418885173828</v>
+        <v>0.006374188781653023</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>47.12656670682107</v>
+        <v>47.12656680809518</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>14.17372298714401</v>
+        <v>14.1737229256177</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.9979275133066693</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.003183945382247713</v>
+        <v>0.003183945354215983</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>38.48273887761444</v>
+        <v>38.48273898635008</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7.9463645255898</v>
+        <v>7.946365366234938</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>1.141736795086661</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.02105877570632486</v>
+        <v>0.02105877556615599</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>50.37570355650195</v>
+        <v>50.37570356125211</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>8.071739603631645</v>
+        <v>8.071739424255387</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>1.591717518967429</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.2737575935030396</v>
+        <v>0.2737575934750045</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>34.63655212079985</v>
+        <v>34.63655192352961</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.61785360486242</v>
+        <v>13.61785357122794</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>1.992951684169262</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.07171242537668543</v>
+        <v>-0.0717124252084802</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>35.74218414138525</v>
+        <v>35.74218412852258</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11.12301228248422</v>
+        <v>11.12301239054997</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>1.760919502465495</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.01614659393724376</v>
+        <v>-0.01614659394285048</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>280.8215544552973</v>
+        <v>280.8215544552968</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>14.9</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>36.44424994528642</v>
+        <v>36.44425013197098</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.67498879254004</v>
+        <v>17.67498879978401</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.5843450739975848</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.007545946962794772</v>
+        <v>-0.007545946948776305</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>279.9882437346843</v>
+        <v>279.9882437346844</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>6.25</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>48.55393282858574</v>
+        <v>48.55393298827664</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>19.11615594113584</v>
+        <v>19.11615594593959</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.2529138567877762</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.01236264550437366</v>
+        <v>0.01236264550156981</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>36.26359385099953</v>
+        <v>36.26359398506199</v>
       </c>
       <c r="I88" s="2" t="n">
         <v>36.43134016052537</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.007032436169860101</v>
+        <v>-0.00703243618387861</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>275.8085682520794</v>
+        <v>275.8085682520796</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>9.859999999999999</v>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>40.88061330824178</v>
+        <v>40.88061350871292</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>19.32283039697867</v>
+        <v>19.32283021562689</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.9656777798966892</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.002733308623751617</v>
+        <v>-0.002733308848023405</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.43435007362613</v>
+        <v>43.43434962107427</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>16.82255521365153</v>
+        <v>16.82255531475795</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>1.169022783709383</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.04150184485276265</v>
+        <v>0.04150184504494409</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>30.2594886590818</v>
+        <v>30.25948882374236</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>34.58904658087221</v>
+        <v>34.58904659993487</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0.6038300506478742</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.009929514370426273</v>
+        <v>0.009929514356408903</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>48.73350263634344</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.06062426556887</v>
+        <v>12.06062414859582</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.2324904627064758</v>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>269.691343074882</v>
+        <v>269.6913430748816</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>15.3</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>35.73061809196055</v>
+        <v>35.73061852203961</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>30.35315976877381</v>
+        <v>30.35315981427476</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>1.253583202524372</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.02073921310322206</v>
+        <v>-0.02073921313125539</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>40.2297815087816</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>40.17210484007352</v>
+        <v>40.17210484439891</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>1.398569821767086</v>
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>255.6636975973329</v>
+        <v>255.6636975973335</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>63.5</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>37.04555218429955</v>
+        <v>37.04555231293152</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.17341359534782</v>
+        <v>15.17341357750499</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.3550157074723045</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.2656956509584859</v>
+        <v>-0.2656956511827586</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>50.99084933536099</v>
+        <v>50.99084933066322</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.79774724240975</v>
+        <v>13.79774726415332</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>1.009326928468627</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.3789605355213391</v>
+        <v>0.3789605355073216</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>247.0535719787305</v>
+        <v>247.0535719787312</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>69.90000000000001</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.13305890940874</v>
+        <v>44.13305899680746</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.70675867097003</v>
+        <v>13.7067587393857</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>1.947212138697003</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.01770878467349235</v>
+        <v>0.01770878447725932</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>246.9234449213294</v>
+        <v>246.9234449213295</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>43.8</v>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>31.78735427169219</v>
+        <v>31.78735372483574</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>24.10910258687021</v>
+        <v>24.10910258792682</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.8609879271902744</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.08278394642341602</v>
+        <v>-0.08278394561043367</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.32820850865157</v>
+        <v>46.3282083954993</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.43046753543922</v>
+        <v>13.43046749088098</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.4522391118085424</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.004306510590113166</v>
+        <v>-0.004306510576095615</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>38.27339308707172</v>
+        <v>38.27339333551261</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.31161572625699</v>
+        <v>18.31161574741834</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.6835417548362436</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0151198826557355</v>
+        <v>-0.01511988269778535</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>234.3729286086362</v>
+        <v>234.3729286086365</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>32.05</v>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>37.17682643631351</v>
+        <v>37.1768269632432</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10.08564701099007</v>
+        <v>10.08564705762232</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.7015852638147142</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.03795846226011274</v>
+        <v>-0.03795846227413339</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>232.7062305274769</v>
+        <v>232.7062305274796</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>96.7</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>31.06818707941413</v>
+        <v>31.0681873661396</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.68040907923018</v>
+        <v>18.68040913097878</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>1.711676728001756</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.3157175437548441</v>
+        <v>-0.3157175438669865</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>231.6225511311849</v>
+        <v>231.6225511311848</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>615</v>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>33.30214368564765</v>
+        <v>33.3021437784537</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.71618488121825</v>
+        <v>12.71618488895323</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.5237464880521181</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-7.221732687026851</v>
+        <v>-7.221732692913974</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.53060187775376</v>
+        <v>41.53060200354995</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>24.7414289684885</v>
+        <v>24.74142898198684</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.4976793908482958</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.05860629757175465</v>
+        <v>-0.05860629758577153</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>51.30613010717237</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>8.699330880273015</v>
+        <v>8.699330913651206</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>1.534455435045157</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>38.00230946826648</v>
+        <v>38.00230951115786</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>17.1794584639681</v>
+        <v>17.17945850692499</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>2.103509245009634</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.003937246065421091</v>
+        <v>0.003937246079439446</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>42.23756932353022</v>
+        <v>42.23756941128819</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.796564315084856</v>
+        <v>9.796564411579839</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.8919521866451359</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.6151077143283727</v>
+        <v>-0.6151077157300788</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>216.5131984072286</v>
+        <v>216.5131984072287</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>13.3</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>39.13823110943726</v>
+        <v>39.13823128478966</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.03879517598908</v>
+        <v>12.03879509252391</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>1.036579126426111</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.001762770009335432</v>
+        <v>0.001762769995320615</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>205.4639235773386</v>
+        <v>205.4639235773384</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>21.55</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.08398949244717</v>
+        <v>47.08398967086807</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>7.494613851280223</v>
+        <v>7.494613856271698</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.7250902417192936</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.009910535161537462</v>
+        <v>0.009910534923249281</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>201.2126428627769</v>
+        <v>201.212642862777</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>26</v>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>35.17635284514378</v>
+        <v>35.17635332073309</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>31.24519962925976</v>
+        <v>31.24519970597999</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.3988081913507854</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.00938773146843086</v>
+        <v>0.0093877312721935</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>194.9523194066122</v>
+        <v>194.9523194066118</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>39.95</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>43.65617313912831</v>
+        <v>43.65617323297415</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.56211252246812</v>
+        <v>17.56211257893873</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.5312389084996308</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.01970664813471337</v>
+        <v>0.01970664803659333</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>193.7034867605876</v>
+        <v>193.7034867605865</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>28.9</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>38.251120029319</v>
+        <v>38.25111964136786</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>22.97816382511045</v>
+        <v>22.97816452947856</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.5314132171035814</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.3378993239871319</v>
+        <v>-0.3378993235385866</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>192.9307045529357</v>
+        <v>192.9307045529352</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>9.710000000000001</v>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>29.31252516957822</v>
+        <v>29.31252522539661</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>22.01298880478296</v>
+        <v>22.01298882918486</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>1.360898114894205</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.01691312567572451</v>
+        <v>-0.01691312568973949</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>38.3210174005151</v>
+        <v>38.32101738765611</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>21.88645097900668</v>
+        <v>21.88645103429687</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>1.001584990708859</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>40.21898436341603</v>
+        <v>40.21898445804143</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>19.15769523305918</v>
+        <v>19.15769534453129</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.1910303369452782</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.01499404685069336</v>
+        <v>0.01499404683667602</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>39.8957435396395</v>
+        <v>39.8957437250638</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>22.60886457362271</v>
+        <v>22.60886461090679</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.5399184266849736</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0942743995079792</v>
+        <v>-0.09427439960609577</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>182.901016227601</v>
+        <v>182.9010162276014</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>6.22</v>
@@ -6650,7 +6650,7 @@
         <v>37.36424647422256</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>23.51100455219949</v>
+        <v>23.51100469886644</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>1.122346288879889</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.01097314850539313</v>
+        <v>-0.0109731485025901</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>181.8618183480426</v>
+        <v>181.8618183480429</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>74.3</v>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>20.77512345552299</v>
+        <v>20.77512239411307</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>36.12172657205576</v>
+        <v>36.1217271163828</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.7811844471055056</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.3064339964838934</v>
+        <v>-0.3064339953625219</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>172.622065604318</v>
+        <v>172.6220656043153</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>12</v>
@@ -6753,7 +6753,7 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>40.41731719505214</v>
+        <v>40.41731717145799</v>
       </c>
       <c r="I119" s="2" t="n">
         <v>20.99784949065089</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.05279314737344756</v>
+        <v>-0.05279314735943069</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>38.74514951413121</v>
+        <v>38.74514951219163</v>
       </c>
       <c r="I120" s="2" t="n">
         <v>17.09814368084951</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>50.06999611718037</v>
+        <v>50.06999625104883</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>5.946345208951548</v>
+        <v>5.946344482879645</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.5098654521723434</v>
@@ -6898,7 +6898,7 @@
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>158.39324731357</v>
+        <v>158.3932473135714</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>9.01</v>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>32.40390734905704</v>
+        <v>32.40390756516165</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>15.84219300251613</v>
+        <v>15.84219298304317</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>1.381537630934448</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.02329689750084775</v>
+        <v>-0.02329689754289752</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>157.5768665362972</v>
+        <v>157.5768665362973</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>14.4</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>43.58614458480404</v>
+        <v>43.58614464424703</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>15.99865273214649</v>
+        <v>15.99865275079692</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.7138346245074088</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.04832510574995136</v>
+        <v>0.04832510573593579</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>42.95216474024279</v>
+        <v>42.95216461466087</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.94059467302017</v>
+        <v>15.94059473872347</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.3061135049663243</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.02715903398230293</v>
+        <v>0.0271590339402525</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>139.4856444413938</v>
+        <v>139.4856444413934</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>18.65</v>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>38.71151293968626</v>
+        <v>38.71151304456053</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>10.4538930990547</v>
+        <v>10.45389313396732</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.6394762684124387</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.002725307383973807</v>
+        <v>-0.002725307454058079</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>139.4479191146526</v>
+        <v>139.4479191146521</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>8.09</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>42.24321417403042</v>
+        <v>42.24321424124142</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>13.37833829015054</v>
+        <v>13.37833818066517</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.4283024881512028</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.003163794723434196</v>
+        <v>0.003163794720629075</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>8.101614084452024</v>
+        <v>8.101614134512275</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>32.26218604406749</v>
+        <v>32.26218610488139</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.08126407941833376</v>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>44.76535378377109</v>
+        <v>44.76535383078174</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>6.053047195481095</v>
+        <v>6.053047258460385</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.8043434055369213</v>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>35.60669350462861</v>
+        <v>35.60669360864836</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>21.45247887624866</v>
+        <v>21.45247884121664</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.3759249138092666</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0352602752841959</v>
+        <v>-0.03526027545239968</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>105.1629217276462</v>
+        <v>105.1629217276461</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>35.2</v>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>36.68310713789047</v>
+        <v>36.68310752702267</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>13.32351274331679</v>
+        <v>13.32351266204702</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.8476287377514268</v>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>42.86656468197072</v>
+        <v>42.86656471572707</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>17.2902323758677</v>
+        <v>17.29023238319868</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.4184158987861103</v>
@@ -7428,7 +7428,7 @@
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>84.39037585176541</v>
+        <v>84.39037585176543</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>27.6</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>37.83218397245656</v>
+        <v>37.83218399930594</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>17.80643321058857</v>
+        <v>17.80643325140756</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.7334442338185182</v>
@@ -7481,7 +7481,7 @@
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>83.83811406728192</v>
+        <v>83.83811406728209</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>0</v>
@@ -7495,7 +7495,7 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>37.10901102455061</v>
+        <v>37.10901102631047</v>
       </c>
       <c r="I133" s="2" t="n">
         <v>8.465557602412245</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-2.825112366861719</v>
+        <v>-2.825112367001884</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
